--- a/research/traditional_assets/database/data/france/france_precious_metals.xlsx
+++ b/research/traditional_assets/database/data/france/france_precious_metals.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="earnings_debt" sheetId="1" r:id="rId1"/>
+    <sheet name="cost_capital" sheetId="2" r:id="rId2"/>
+    <sheet name="enxtpa_mlbat" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -588,46 +590,46 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.2185</v>
+        <v>-0.13155</v>
       </c>
       <c r="E2">
-        <v>-0.119</v>
+        <v>-0.10945</v>
       </c>
       <c r="G2">
-        <v>1.209510869565218</v>
+        <v>0.5992935635792779</v>
       </c>
       <c r="H2">
-        <v>1.209510869565218</v>
+        <v>0.5992935635792779</v>
       </c>
       <c r="I2">
-        <v>0.6413043478260869</v>
+        <v>0.7155808477237049</v>
       </c>
       <c r="J2">
-        <v>0.5411622073578596</v>
+        <v>0.4703392959229045</v>
       </c>
       <c r="K2">
-        <v>8.244000000000002</v>
+        <v>12.53</v>
       </c>
       <c r="L2">
-        <v>0.4480434782608697</v>
+        <v>0.4917582417582417</v>
       </c>
       <c r="M2">
-        <v>18.1</v>
+        <v>15.3</v>
       </c>
       <c r="N2">
-        <v>0.08791102044781195</v>
+        <v>0.0773156804285209</v>
       </c>
       <c r="O2">
-        <v>2.195536147501213</v>
+        <v>1.221069433359936</v>
       </c>
       <c r="P2">
-        <v>18.1</v>
+        <v>15.3</v>
       </c>
       <c r="Q2">
-        <v>0.08791102044781195</v>
+        <v>0.0773156804285209</v>
       </c>
       <c r="R2">
-        <v>2.195536147501213</v>
+        <v>1.221069433359936</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,19 +638,19 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>27.7</v>
+        <v>18.8</v>
       </c>
       <c r="V2">
-        <v>0.134537860022342</v>
+        <v>0.09500227399060084</v>
       </c>
       <c r="X2">
-        <v>0.05948030376615032</v>
+        <v>0.1134718995454789</v>
       </c>
       <c r="Z2">
-        <v>1.069767441860465</v>
+        <v>1.525748502994012</v>
       </c>
       <c r="AB2">
-        <v>0.05948030376615032</v>
+        <v>0.1134718995454789</v>
       </c>
       <c r="AD2">
         <v>0</v>
@@ -660,7 +662,7 @@
         <v>0</v>
       </c>
       <c r="AG2">
-        <v>-27.7</v>
+        <v>-18.8</v>
       </c>
       <c r="AH2">
         <v>0</v>
@@ -669,28 +671,28 @@
         <v>0</v>
       </c>
       <c r="AJ2">
-        <v>-0.1554520455693361</v>
+        <v>-0.1049751521581328</v>
       </c>
       <c r="AK2">
-        <v>-1.658682634730539</v>
+        <v>-0.9740932642487047</v>
       </c>
       <c r="AL2">
-        <v>0.014</v>
+        <v>0.007</v>
       </c>
       <c r="AM2">
-        <v>-0.126</v>
+        <v>-0.145</v>
       </c>
       <c r="AN2">
         <v>0</v>
       </c>
       <c r="AO2">
-        <v>842.8571428571428</v>
+        <v>2604.714285714286</v>
       </c>
       <c r="AP2">
-        <v>-2.138170590505596</v>
+        <v>-0.9806990088680229</v>
       </c>
       <c r="AQ2">
-        <v>-93.65079365079364</v>
+        <v>-125.7448275862069</v>
       </c>
     </row>
     <row r="3">
@@ -701,7 +703,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>EURO Ressources S.A. (ENXTPA:EUR)</t>
+          <t>Batla Minerals SA (ENXTPA:MLBAT)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -710,79 +712,61 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.129</v>
+        <v>-0.193</v>
       </c>
       <c r="E3">
-        <v>-0.119</v>
+        <v>-0.154</v>
       </c>
       <c r="G3">
-        <v>1.614285714285714</v>
+        <v>0.2293956043956044</v>
       </c>
       <c r="H3">
-        <v>1.614285714285714</v>
+        <v>0.2293956043956044</v>
       </c>
       <c r="I3">
-        <v>0.9357142857142857</v>
+        <v>0.1281593406593407</v>
       </c>
       <c r="J3">
-        <v>0.6434835164835165</v>
+        <v>0.08202197802197804</v>
       </c>
       <c r="K3">
-        <v>8.960000000000001</v>
+        <v>0.83</v>
       </c>
       <c r="L3">
-        <v>0.64</v>
+        <v>0.114010989010989</v>
       </c>
       <c r="M3">
-        <v>18.1</v>
+        <v>-0</v>
       </c>
       <c r="N3">
-        <v>0.08938271604938272</v>
+        <v>-0</v>
       </c>
       <c r="O3">
-        <v>2.020089285714286</v>
+        <v>-0</v>
       </c>
       <c r="P3">
-        <v>18.1</v>
+        <v>-0</v>
       </c>
       <c r="Q3">
-        <v>0.08938271604938272</v>
+        <v>-0</v>
       </c>
       <c r="R3">
-        <v>2.020089285714286</v>
+        <v>-0</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
-      <c r="T3">
-        <v>0</v>
-      </c>
       <c r="U3">
-        <v>27.7</v>
+        <v>0</v>
       </c>
       <c r="V3">
-        <v>0.1367901234567901</v>
-      </c>
-      <c r="W3">
-        <v>0.1700189753320683</v>
+        <v>0</v>
       </c>
       <c r="X3">
-        <v>0.05948030376615032</v>
-      </c>
-      <c r="Y3">
-        <v>0.110538671565918</v>
-      </c>
-      <c r="Z3">
-        <v>0.8139534883720929</v>
-      </c>
-      <c r="AA3">
-        <v>0.5237656529516993</v>
+        <v>0.1134718995454789</v>
       </c>
       <c r="AB3">
-        <v>0.05948030376615032</v>
-      </c>
-      <c r="AC3">
-        <v>0.464285349185549</v>
+        <v>0.1134718995454789</v>
       </c>
       <c r="AD3">
         <v>0</v>
@@ -794,34 +778,31 @@
         <v>0</v>
       </c>
       <c r="AG3">
-        <v>-27.7</v>
+        <v>0</v>
       </c>
       <c r="AH3">
         <v>0</v>
       </c>
-      <c r="AI3">
-        <v>0</v>
-      </c>
       <c r="AJ3">
-        <v>-0.158466819221968</v>
-      </c>
-      <c r="AK3">
-        <v>-1.658682634730539</v>
+        <v>0</v>
       </c>
       <c r="AL3">
-        <v>0</v>
+        <v>0.007</v>
       </c>
       <c r="AM3">
-        <v>-0.14</v>
+        <v>0.007</v>
       </c>
       <c r="AN3">
         <v>0</v>
       </c>
+      <c r="AO3">
+        <v>133.2857142857143</v>
+      </c>
       <c r="AP3">
-        <v>-2.082706766917293</v>
+        <v>0</v>
       </c>
       <c r="AQ3">
-        <v>-93.57142857142856</v>
+        <v>133.2857142857143</v>
       </c>
     </row>
     <row r="4">
@@ -832,103 +813,8836 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
+          <t>EURO Ressources S.A. (ENXTPA:EUR)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Precious Metals</t>
+        </is>
+      </c>
+      <c r="D4">
+        <v>-0.0701</v>
+      </c>
+      <c r="E4">
+        <v>-0.0649</v>
+      </c>
+      <c r="G4">
+        <v>0.7472527472527473</v>
+      </c>
+      <c r="H4">
+        <v>0.7472527472527473</v>
+      </c>
+      <c r="I4">
+        <v>0.9505494505494506</v>
+      </c>
+      <c r="J4">
+        <v>0.6412087912087914</v>
+      </c>
+      <c r="K4">
+        <v>11.7</v>
+      </c>
+      <c r="L4">
+        <v>0.6428571428571428</v>
+      </c>
+      <c r="M4">
+        <v>15.3</v>
+      </c>
+      <c r="N4">
+        <v>0.07794192562404482</v>
+      </c>
+      <c r="O4">
+        <v>1.307692307692308</v>
+      </c>
+      <c r="P4">
+        <v>15.3</v>
+      </c>
+      <c r="Q4">
+        <v>0.07794192562404482</v>
+      </c>
+      <c r="R4">
+        <v>1.307692307692308</v>
+      </c>
+      <c r="S4">
+        <v>0</v>
+      </c>
+      <c r="T4">
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <v>18.8</v>
+      </c>
+      <c r="V4">
+        <v>0.09577177789098319</v>
+      </c>
+      <c r="W4">
+        <v>0.2635135135135135</v>
+      </c>
+      <c r="X4">
+        <v>0.1134718995454789</v>
+      </c>
+      <c r="Y4">
+        <v>0.1500416139680346</v>
+      </c>
+      <c r="Z4">
+        <v>1.089820359281437</v>
+      </c>
+      <c r="AA4">
+        <v>0.698802395209581</v>
+      </c>
+      <c r="AB4">
+        <v>0.1134718995454789</v>
+      </c>
+      <c r="AC4">
+        <v>0.5853304956641021</v>
+      </c>
+      <c r="AD4">
+        <v>0</v>
+      </c>
+      <c r="AE4">
+        <v>0</v>
+      </c>
+      <c r="AF4">
+        <v>0</v>
+      </c>
+      <c r="AG4">
+        <v>-18.8</v>
+      </c>
+      <c r="AH4">
+        <v>0</v>
+      </c>
+      <c r="AI4">
+        <v>0</v>
+      </c>
+      <c r="AJ4">
+        <v>-0.1059154929577465</v>
+      </c>
+      <c r="AK4">
+        <v>-0.9740932642487047</v>
+      </c>
+      <c r="AL4">
+        <v>0</v>
+      </c>
+      <c r="AM4">
+        <v>-0.152</v>
+      </c>
+      <c r="AN4">
+        <v>0</v>
+      </c>
+      <c r="AP4">
+        <v>-1.074285714285714</v>
+      </c>
+      <c r="AQ4">
+        <v>-113.8157894736842</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AQ2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>company_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>exchange_ticker</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>industry_group</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_capital</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_capital</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>actual_equity_value</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_equity_value</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>actual_enterprise_value</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_enterprise_value</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_capital</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_capital</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_rating</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_rating</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_equity</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>actual_beta</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_beta</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>country_default_spread</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>risk_free</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>market_capitalization</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_risk_premium</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>marginal_tax_rate</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_max_percentage</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_method</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_ebitda</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_depreciation</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>reported_capital_spending</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_debt</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_mv_debt</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>reported_interest_expense</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>reported_bv_debt</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>reported_cash</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>flag_bankruptcy</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>flag_refinanced</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>rating_firm_type</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
           <t>Batla Minerals SA (ENXTPA:MLBAT)</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>ENXTPA:MLBAT</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
         <is>
           <t>Precious Metals</t>
         </is>
       </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
+        <v>0.98</v>
+      </c>
+      <c r="G2">
+        <v>1.59</v>
+      </c>
+      <c r="H2">
+        <v>0.119999170192462</v>
+      </c>
+      <c r="I2">
+        <v>1.59</v>
+      </c>
+      <c r="J2">
+        <v>1.67819917019246</v>
+      </c>
+      <c r="K2">
+        <v>0</v>
+      </c>
+      <c r="L2">
+        <v>1.5582</v>
+      </c>
+      <c r="M2">
+        <v>0.113471899545479</v>
+      </c>
+      <c r="N2">
+        <v>0.09074278415683661</v>
+      </c>
+      <c r="O2">
+        <v>0.0730799311926605</v>
+      </c>
+      <c r="P2">
+        <v>0.034275</v>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="S2">
+        <v>0.113471899545479</v>
+      </c>
+      <c r="T2">
+        <v>2.85766420784182</v>
+      </c>
+      <c r="U2">
+        <v>1.1035944406135</v>
+      </c>
+      <c r="V2">
+        <v>41.6606901331595</v>
+      </c>
+      <c r="W2">
+        <v>13.04596814986264</v>
+      </c>
+      <c r="X2">
+        <v>0</v>
+      </c>
+      <c r="Y2">
+        <v>0</v>
+      </c>
+      <c r="Z2">
+        <v>0.0388</v>
+      </c>
+      <c r="AA2">
+        <v>1.59</v>
+      </c>
+      <c r="AB2">
+        <v>0.06766244627325971</v>
+      </c>
+      <c r="AC2">
+        <v>0.09743990825688073</v>
+      </c>
+      <c r="AD2">
+        <v>0.2500000000000001</v>
+      </c>
+      <c r="AE2">
+        <v>0</v>
+      </c>
+      <c r="AF2">
+        <v>1</v>
+      </c>
+      <c r="AG2">
+        <v>1.67</v>
+      </c>
+      <c r="AH2">
+        <v>0.741</v>
+      </c>
+      <c r="AI2">
+        <v>0.428</v>
+      </c>
+      <c r="AJ2">
+        <v>0</v>
+      </c>
+      <c r="AK2">
+        <v>0</v>
+      </c>
+      <c r="AL2">
+        <v>0.007</v>
+      </c>
+      <c r="AN2">
+        <v>0</v>
+      </c>
+      <c r="AO2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AP2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ2">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Z101"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>debt_capital</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>cost_capital</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>equity_value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>enterprise_value</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>debt_issued</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>debt</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>marketcap</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>drop_ebitda</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ebitda</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>depreciation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ebit</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>interest_expense</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>taxable_income</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>taxes</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>net_income</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>operating_cash_flow</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>debt_equity</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>tax_rate</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>debt_rating</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0.1134718995454789</v>
+      </c>
+      <c r="C2">
+        <v>1.59</v>
+      </c>
+      <c r="D2">
+        <v>1.59</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>0</v>
+      </c>
+      <c r="H2">
+        <v>1.59</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>1.67</v>
+      </c>
+      <c r="K2">
+        <v>0.741</v>
+      </c>
+      <c r="L2">
+        <v>0.9289999999999999</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>0.9289999999999999</v>
+      </c>
+      <c r="O2">
+        <v>0.2322500000000001</v>
+      </c>
+      <c r="P2">
+        <v>0.6967499999999999</v>
+      </c>
+      <c r="Q2">
+        <v>1.43775</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0.1134718995454789</v>
+      </c>
+      <c r="T2">
+        <v>1.103594440613497</v>
+      </c>
+      <c r="U2">
+        <v>0.0457</v>
+      </c>
+      <c r="V2">
+        <v>0.2500000000000001</v>
+      </c>
+      <c r="W2">
+        <v>0.034275</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y2">
+        <v>10000000</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>0.01</v>
+      </c>
+      <c r="B3">
+        <v>0.1132399697966152</v>
+      </c>
+      <c r="C3">
+        <v>1.574953149250296</v>
+      </c>
+      <c r="D3">
+        <v>1.590853149250296</v>
+      </c>
+      <c r="E3">
+        <v>0.0159</v>
+      </c>
+      <c r="F3">
+        <v>0.0159</v>
+      </c>
+      <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3">
+        <v>1.59</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>1.67</v>
+      </c>
+      <c r="K3">
+        <v>0.741</v>
+      </c>
+      <c r="L3">
+        <v>0.9289999999999999</v>
+      </c>
+      <c r="M3">
+        <v>0.0007266300000000001</v>
+      </c>
+      <c r="N3">
+        <v>0.92827337</v>
+      </c>
+      <c r="O3">
+        <v>0.2320683425000001</v>
+      </c>
+      <c r="P3">
+        <v>0.6962050274999999</v>
+      </c>
+      <c r="Q3">
+        <v>1.4372050275</v>
+      </c>
+      <c r="R3">
+        <v>0.0101010101010101</v>
+      </c>
+      <c r="S3">
+        <v>0.1140375957541567</v>
+      </c>
+      <c r="T3">
+        <v>1.111955004557539</v>
+      </c>
+      <c r="U3">
+        <v>0.0457</v>
+      </c>
+      <c r="V3">
+        <v>0.2500000000000001</v>
+      </c>
+      <c r="W3">
+        <v>0.034275</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y3">
+        <v>1278.504878686539</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>0.02</v>
+      </c>
+      <c r="B4">
+        <v>0.1130080400477515</v>
+      </c>
+      <c r="C4">
+        <v>1.559907214543868</v>
+      </c>
       <c r="D4">
-        <v>-0.308</v>
+        <v>1.591707214543868</v>
+      </c>
+      <c r="E4">
+        <v>0.0318</v>
+      </c>
+      <c r="F4">
+        <v>0.0318</v>
       </c>
       <c r="G4">
-        <v>-0.0784090909090909</v>
+        <v>0</v>
       </c>
       <c r="H4">
-        <v>-0.0784090909090909</v>
+        <v>1.59</v>
       </c>
       <c r="I4">
-        <v>-0.2954545454545454</v>
+        <v>0</v>
       </c>
       <c r="J4">
-        <v>-0.2954545454545454</v>
+        <v>1.67</v>
       </c>
       <c r="K4">
-        <v>-0.716</v>
+        <v>0.741</v>
       </c>
       <c r="L4">
-        <v>-0.1627272727272727</v>
+        <v>0.9289999999999999</v>
       </c>
       <c r="M4">
-        <v>-0</v>
+        <v>0.00145326</v>
       </c>
       <c r="N4">
-        <v>-0</v>
+        <v>0.9275467399999999</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>0.2318866850000001</v>
       </c>
       <c r="P4">
-        <v>-0</v>
+        <v>0.6956600549999998</v>
       </c>
       <c r="Q4">
-        <v>-0</v>
+        <v>1.436660055</v>
       </c>
       <c r="R4">
-        <v>0</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>0.1146148367834199</v>
+      </c>
+      <c r="T4">
+        <v>1.120486192255541</v>
       </c>
       <c r="U4">
-        <v>0</v>
+        <v>0.0457</v>
       </c>
       <c r="V4">
-        <v>0</v>
-      </c>
-      <c r="X4">
-        <v>0.05948030376615032</v>
-      </c>
-      <c r="AB4">
-        <v>0.05948030376615032</v>
-      </c>
-      <c r="AD4">
-        <v>0</v>
-      </c>
-      <c r="AE4">
-        <v>0</v>
-      </c>
-      <c r="AF4">
-        <v>0</v>
-      </c>
-      <c r="AG4">
-        <v>0</v>
-      </c>
-      <c r="AH4">
-        <v>0</v>
-      </c>
-      <c r="AJ4">
-        <v>0</v>
-      </c>
-      <c r="AL4">
-        <v>0.014</v>
-      </c>
-      <c r="AM4">
-        <v>0.014</v>
-      </c>
-      <c r="AN4">
-        <v>-0</v>
-      </c>
-      <c r="AO4">
-        <v>-92.85714285714286</v>
-      </c>
-      <c r="AP4">
-        <v>-0</v>
-      </c>
-      <c r="AQ4">
-        <v>-92.85714285714286</v>
+        <v>0.2500000000000001</v>
+      </c>
+      <c r="W4">
+        <v>0.034275</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y4">
+        <v>639.2524393432694</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>0.03</v>
+      </c>
+      <c r="B5">
+        <v>0.1127761102988878</v>
+      </c>
+      <c r="C5">
+        <v>1.544862197356869</v>
+      </c>
+      <c r="D5">
+        <v>1.592562197356869</v>
+      </c>
+      <c r="E5">
+        <v>0.0477</v>
+      </c>
+      <c r="F5">
+        <v>0.0477</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>1.59</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>1.67</v>
+      </c>
+      <c r="K5">
+        <v>0.741</v>
+      </c>
+      <c r="L5">
+        <v>0.9289999999999999</v>
+      </c>
+      <c r="M5">
+        <v>0.00217989</v>
+      </c>
+      <c r="N5">
+        <v>0.92682011</v>
+      </c>
+      <c r="O5">
+        <v>0.2317050275000001</v>
+      </c>
+      <c r="P5">
+        <v>0.6951150824999999</v>
+      </c>
+      <c r="Q5">
+        <v>1.4361150825</v>
+      </c>
+      <c r="R5">
+        <v>0.03092783505154639</v>
+      </c>
+      <c r="S5">
+        <v>0.115203979689575</v>
+      </c>
+      <c r="T5">
+        <v>1.129193280730821</v>
+      </c>
+      <c r="U5">
+        <v>0.0457</v>
+      </c>
+      <c r="V5">
+        <v>0.2500000000000001</v>
+      </c>
+      <c r="W5">
+        <v>0.034275</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y5">
+        <v>426.168292895513</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>0.04</v>
+      </c>
+      <c r="B6">
+        <v>0.1125441805500241</v>
+      </c>
+      <c r="C6">
+        <v>1.529818099168625</v>
+      </c>
+      <c r="D6">
+        <v>1.593418099168625</v>
+      </c>
+      <c r="E6">
+        <v>0.0636</v>
+      </c>
+      <c r="F6">
+        <v>0.0636</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>1.59</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>1.67</v>
+      </c>
+      <c r="K6">
+        <v>0.741</v>
+      </c>
+      <c r="L6">
+        <v>0.9289999999999999</v>
+      </c>
+      <c r="M6">
+        <v>0.002906520000000001</v>
+      </c>
+      <c r="N6">
+        <v>0.9260934799999999</v>
+      </c>
+      <c r="O6">
+        <v>0.2315233700000001</v>
+      </c>
+      <c r="P6">
+        <v>0.6945701099999998</v>
+      </c>
+      <c r="Q6">
+        <v>1.43557011</v>
+      </c>
+      <c r="R6">
+        <v>0.04166666666666667</v>
+      </c>
+      <c r="S6">
+        <v>0.1158053964062751</v>
+      </c>
+      <c r="T6">
+        <v>1.138081766882669</v>
+      </c>
+      <c r="U6">
+        <v>0.0457</v>
+      </c>
+      <c r="V6">
+        <v>0.2500000000000001</v>
+      </c>
+      <c r="W6">
+        <v>0.034275</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y6">
+        <v>319.6262196716347</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>0.05</v>
+      </c>
+      <c r="B7">
+        <v>0.1123122508011604</v>
+      </c>
+      <c r="C7">
+        <v>1.514774921461645</v>
+      </c>
+      <c r="D7">
+        <v>1.594274921461645</v>
+      </c>
+      <c r="E7">
+        <v>0.07950000000000002</v>
+      </c>
+      <c r="F7">
+        <v>0.07950000000000002</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>1.59</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>1.67</v>
+      </c>
+      <c r="K7">
+        <v>0.741</v>
+      </c>
+      <c r="L7">
+        <v>0.9289999999999999</v>
+      </c>
+      <c r="M7">
+        <v>0.003633150000000001</v>
+      </c>
+      <c r="N7">
+        <v>0.92536685</v>
+      </c>
+      <c r="O7">
+        <v>0.2313417125000001</v>
+      </c>
+      <c r="P7">
+        <v>0.6940251374999998</v>
+      </c>
+      <c r="Q7">
+        <v>1.4350251375</v>
+      </c>
+      <c r="R7">
+        <v>0.05263157894736843</v>
+      </c>
+      <c r="S7">
+        <v>0.1164194745275372</v>
+      </c>
+      <c r="T7">
+        <v>1.147157379058767</v>
+      </c>
+      <c r="U7">
+        <v>0.0457</v>
+      </c>
+      <c r="V7">
+        <v>0.2500000000000001</v>
+      </c>
+      <c r="W7">
+        <v>0.034275</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y7">
+        <v>255.7009757373077</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>0.06</v>
+      </c>
+      <c r="B8">
+        <v>0.1120803210522967</v>
+      </c>
+      <c r="C8">
+        <v>1.499732665721628</v>
+      </c>
+      <c r="D8">
+        <v>1.595132665721628</v>
+      </c>
+      <c r="E8">
+        <v>0.0954</v>
+      </c>
+      <c r="F8">
+        <v>0.0954</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <v>1.59</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>1.67</v>
+      </c>
+      <c r="K8">
+        <v>0.741</v>
+      </c>
+      <c r="L8">
+        <v>0.9289999999999999</v>
+      </c>
+      <c r="M8">
+        <v>0.004359780000000001</v>
+      </c>
+      <c r="N8">
+        <v>0.9246402199999999</v>
+      </c>
+      <c r="O8">
+        <v>0.2311600550000001</v>
+      </c>
+      <c r="P8">
+        <v>0.6934801649999998</v>
+      </c>
+      <c r="Q8">
+        <v>1.434480165</v>
+      </c>
+      <c r="R8">
+        <v>0.06382978723404255</v>
+      </c>
+      <c r="S8">
+        <v>0.1170466181407412</v>
+      </c>
+      <c r="T8">
+        <v>1.156426089366271</v>
+      </c>
+      <c r="U8">
+        <v>0.0457</v>
+      </c>
+      <c r="V8">
+        <v>0.2500000000000001</v>
+      </c>
+      <c r="W8">
+        <v>0.034275</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y8">
+        <v>213.0841464477565</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="B9">
+        <v>0.111848391303433</v>
+      </c>
+      <c r="C9">
+        <v>1.484691333437471</v>
+      </c>
+      <c r="D9">
+        <v>1.595991333437471</v>
+      </c>
+      <c r="E9">
+        <v>0.1113</v>
+      </c>
+      <c r="F9">
+        <v>0.1113</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <v>1.59</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>1.67</v>
+      </c>
+      <c r="K9">
+        <v>0.741</v>
+      </c>
+      <c r="L9">
+        <v>0.9289999999999999</v>
+      </c>
+      <c r="M9">
+        <v>0.005086410000000001</v>
+      </c>
+      <c r="N9">
+        <v>0.92391359</v>
+      </c>
+      <c r="O9">
+        <v>0.2309783975000001</v>
+      </c>
+      <c r="P9">
+        <v>0.6929351924999998</v>
+      </c>
+      <c r="Q9">
+        <v>1.4339351925</v>
+      </c>
+      <c r="R9">
+        <v>0.07526881720430109</v>
+      </c>
+      <c r="S9">
+        <v>0.1176872487133688</v>
+      </c>
+      <c r="T9">
+        <v>1.165894126777163</v>
+      </c>
+      <c r="U9">
+        <v>0.0457</v>
+      </c>
+      <c r="V9">
+        <v>0.2500000000000001</v>
+      </c>
+      <c r="W9">
+        <v>0.034275</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y9">
+        <v>182.643554098077</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>0.08</v>
+      </c>
+      <c r="B10">
+        <v>0.1116164615545693</v>
+      </c>
+      <c r="C10">
+        <v>1.469650926101281</v>
+      </c>
+      <c r="D10">
+        <v>1.596850926101281</v>
+      </c>
+      <c r="E10">
+        <v>0.1272</v>
+      </c>
+      <c r="F10">
+        <v>0.1272</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10">
+        <v>1.59</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>1.67</v>
+      </c>
+      <c r="K10">
+        <v>0.741</v>
+      </c>
+      <c r="L10">
+        <v>0.9289999999999999</v>
+      </c>
+      <c r="M10">
+        <v>0.005813040000000001</v>
+      </c>
+      <c r="N10">
+        <v>0.9231869599999999</v>
+      </c>
+      <c r="O10">
+        <v>0.2307967400000001</v>
+      </c>
+      <c r="P10">
+        <v>0.6923902199999998</v>
+      </c>
+      <c r="Q10">
+        <v>1.43339022</v>
+      </c>
+      <c r="R10">
+        <v>0.08695652173913043</v>
+      </c>
+      <c r="S10">
+        <v>0.1183418060375753</v>
+      </c>
+      <c r="T10">
+        <v>1.175567991088291</v>
+      </c>
+      <c r="U10">
+        <v>0.0457</v>
+      </c>
+      <c r="V10">
+        <v>0.2500000000000001</v>
+      </c>
+      <c r="W10">
+        <v>0.034275</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y10">
+        <v>159.8131098358174</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>0.09</v>
+      </c>
+      <c r="B11">
+        <v>0.1113845318057056</v>
+      </c>
+      <c r="C11">
+        <v>1.45461144520838</v>
+      </c>
+      <c r="D11">
+        <v>1.59771144520838</v>
+      </c>
+      <c r="E11">
+        <v>0.1431</v>
+      </c>
+      <c r="F11">
+        <v>0.1431</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11">
+        <v>1.59</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>1.67</v>
+      </c>
+      <c r="K11">
+        <v>0.741</v>
+      </c>
+      <c r="L11">
+        <v>0.9289999999999999</v>
+      </c>
+      <c r="M11">
+        <v>0.006539670000000001</v>
+      </c>
+      <c r="N11">
+        <v>0.9224603299999999</v>
+      </c>
+      <c r="O11">
+        <v>0.2306150825000001</v>
+      </c>
+      <c r="P11">
+        <v>0.6918452474999999</v>
+      </c>
+      <c r="Q11">
+        <v>1.4328452475</v>
+      </c>
+      <c r="R11">
+        <v>0.0989010989010989</v>
+      </c>
+      <c r="S11">
+        <v>0.1190107492370391</v>
+      </c>
+      <c r="T11">
+        <v>1.185454467801861</v>
+      </c>
+      <c r="U11">
+        <v>0.0457</v>
+      </c>
+      <c r="V11">
+        <v>0.2500000000000001</v>
+      </c>
+      <c r="W11">
+        <v>0.034275</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y11">
+        <v>142.0560976318377</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>0.1</v>
+      </c>
+      <c r="B12">
+        <v>0.1111526020568419</v>
+      </c>
+      <c r="C12">
+        <v>1.439572892257314</v>
+      </c>
+      <c r="D12">
+        <v>1.598572892257314</v>
+      </c>
+      <c r="E12">
+        <v>0.159</v>
+      </c>
+      <c r="F12">
+        <v>0.159</v>
+      </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12">
+        <v>1.59</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>1.67</v>
+      </c>
+      <c r="K12">
+        <v>0.741</v>
+      </c>
+      <c r="L12">
+        <v>0.9289999999999999</v>
+      </c>
+      <c r="M12">
+        <v>0.007266300000000002</v>
+      </c>
+      <c r="N12">
+        <v>0.9217337</v>
+      </c>
+      <c r="O12">
+        <v>0.2304334250000001</v>
+      </c>
+      <c r="P12">
+        <v>0.6913002749999999</v>
+      </c>
+      <c r="Q12">
+        <v>1.432300275</v>
+      </c>
+      <c r="R12">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="S12">
+        <v>0.1196945578409354</v>
+      </c>
+      <c r="T12">
+        <v>1.195560643997955</v>
+      </c>
+      <c r="U12">
+        <v>0.0457</v>
+      </c>
+      <c r="V12">
+        <v>0.2500000000000001</v>
+      </c>
+      <c r="W12">
+        <v>0.034275</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y12">
+        <v>127.8504878686539</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>0.11</v>
+      </c>
+      <c r="B13">
+        <v>0.1109206723079782</v>
+      </c>
+      <c r="C13">
+        <v>1.424535268749863</v>
+      </c>
+      <c r="D13">
+        <v>1.599435268749863</v>
+      </c>
+      <c r="E13">
+        <v>0.1749</v>
+      </c>
+      <c r="F13">
+        <v>0.1749</v>
+      </c>
+      <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="H13">
+        <v>1.59</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>1.67</v>
+      </c>
+      <c r="K13">
+        <v>0.741</v>
+      </c>
+      <c r="L13">
+        <v>0.9289999999999999</v>
+      </c>
+      <c r="M13">
+        <v>0.007992930000000001</v>
+      </c>
+      <c r="N13">
+        <v>0.9210070699999999</v>
+      </c>
+      <c r="O13">
+        <v>0.2302517675000001</v>
+      </c>
+      <c r="P13">
+        <v>0.6907553024999998</v>
+      </c>
+      <c r="Q13">
+        <v>1.4317553025</v>
+      </c>
+      <c r="R13">
+        <v>0.1235955056179775</v>
+      </c>
+      <c r="S13">
+        <v>0.1203937329303126</v>
+      </c>
+      <c r="T13">
+        <v>1.205893925277108</v>
+      </c>
+      <c r="U13">
+        <v>0.0457</v>
+      </c>
+      <c r="V13">
+        <v>0.2500000000000001</v>
+      </c>
+      <c r="W13">
+        <v>0.034275</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y13">
+        <v>116.2277162442308</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>0.12</v>
+      </c>
+      <c r="B14">
+        <v>0.1106887425591145</v>
+      </c>
+      <c r="C14">
+        <v>1.409498576191052</v>
+      </c>
+      <c r="D14">
+        <v>1.600298576191052</v>
+      </c>
+      <c r="E14">
+        <v>0.1908</v>
+      </c>
+      <c r="F14">
+        <v>0.1908</v>
+      </c>
+      <c r="G14">
+        <v>0</v>
+      </c>
+      <c r="H14">
+        <v>1.59</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>1.67</v>
+      </c>
+      <c r="K14">
+        <v>0.741</v>
+      </c>
+      <c r="L14">
+        <v>0.9289999999999999</v>
+      </c>
+      <c r="M14">
+        <v>0.008719560000000001</v>
+      </c>
+      <c r="N14">
+        <v>0.92028044</v>
+      </c>
+      <c r="O14">
+        <v>0.2300701100000001</v>
+      </c>
+      <c r="P14">
+        <v>0.6902103299999999</v>
+      </c>
+      <c r="Q14">
+        <v>1.43121033</v>
+      </c>
+      <c r="R14">
+        <v>0.1363636363636364</v>
+      </c>
+      <c r="S14">
+        <v>0.1211087983626301</v>
+      </c>
+      <c r="T14">
+        <v>1.21646205385806</v>
+      </c>
+      <c r="U14">
+        <v>0.0457</v>
+      </c>
+      <c r="V14">
+        <v>0.2500000000000001</v>
+      </c>
+      <c r="W14">
+        <v>0.034275</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y14">
+        <v>106.5420732238782</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>0.13</v>
+      </c>
+      <c r="B15">
+        <v>0.1104568128102508</v>
+      </c>
+      <c r="C15">
+        <v>1.394462816089153</v>
+      </c>
+      <c r="D15">
+        <v>1.601162816089154</v>
+      </c>
+      <c r="E15">
+        <v>0.2067</v>
+      </c>
+      <c r="F15">
+        <v>0.2067</v>
+      </c>
+      <c r="G15">
+        <v>0</v>
+      </c>
+      <c r="H15">
+        <v>1.59</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>1.67</v>
+      </c>
+      <c r="K15">
+        <v>0.741</v>
+      </c>
+      <c r="L15">
+        <v>0.9289999999999999</v>
+      </c>
+      <c r="M15">
+        <v>0.009446190000000002</v>
+      </c>
+      <c r="N15">
+        <v>0.9195538099999999</v>
+      </c>
+      <c r="O15">
+        <v>0.2298884525000001</v>
+      </c>
+      <c r="P15">
+        <v>0.6896653574999998</v>
+      </c>
+      <c r="Q15">
+        <v>1.4306653575</v>
+      </c>
+      <c r="R15">
+        <v>0.1494252873563219</v>
+      </c>
+      <c r="S15">
+        <v>0.121840302080748</v>
+      </c>
+      <c r="T15">
+        <v>1.227273127923631</v>
+      </c>
+      <c r="U15">
+        <v>0.0457</v>
+      </c>
+      <c r="V15">
+        <v>0.2500000000000001</v>
+      </c>
+      <c r="W15">
+        <v>0.034275</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y15">
+        <v>98.34652912973375</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>0.14</v>
+      </c>
+      <c r="B16">
+        <v>0.1102248830613871</v>
+      </c>
+      <c r="C16">
+        <v>1.379427989955702</v>
+      </c>
+      <c r="D16">
+        <v>1.602027989955702</v>
+      </c>
+      <c r="E16">
+        <v>0.2226</v>
+      </c>
+      <c r="F16">
+        <v>0.2226</v>
+      </c>
+      <c r="G16">
+        <v>0</v>
+      </c>
+      <c r="H16">
+        <v>1.59</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>1.67</v>
+      </c>
+      <c r="K16">
+        <v>0.741</v>
+      </c>
+      <c r="L16">
+        <v>0.9289999999999999</v>
+      </c>
+      <c r="M16">
+        <v>0.01017282</v>
+      </c>
+      <c r="N16">
+        <v>0.91882718</v>
+      </c>
+      <c r="O16">
+        <v>0.2297067950000001</v>
+      </c>
+      <c r="P16">
+        <v>0.6891203849999998</v>
+      </c>
+      <c r="Q16">
+        <v>1.430120385</v>
+      </c>
+      <c r="R16">
+        <v>0.1627906976744186</v>
+      </c>
+      <c r="S16">
+        <v>0.1225888175132408</v>
+      </c>
+      <c r="T16">
+        <v>1.238335622316308</v>
+      </c>
+      <c r="U16">
+        <v>0.0457</v>
+      </c>
+      <c r="V16">
+        <v>0.2500000000000001</v>
+      </c>
+      <c r="W16">
+        <v>0.034275</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y16">
+        <v>91.32177704903849</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>0.15</v>
+      </c>
+      <c r="B17">
+        <v>0.1099929533125234</v>
+      </c>
+      <c r="C17">
+        <v>1.364394099305499</v>
+      </c>
+      <c r="D17">
+        <v>1.602894099305499</v>
+      </c>
+      <c r="E17">
+        <v>0.2385</v>
+      </c>
+      <c r="F17">
+        <v>0.2385</v>
+      </c>
+      <c r="G17">
+        <v>0</v>
+      </c>
+      <c r="H17">
+        <v>1.59</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>1.67</v>
+      </c>
+      <c r="K17">
+        <v>0.741</v>
+      </c>
+      <c r="L17">
+        <v>0.9289999999999999</v>
+      </c>
+      <c r="M17">
+        <v>0.01089945</v>
+      </c>
+      <c r="N17">
+        <v>0.9181005499999999</v>
+      </c>
+      <c r="O17">
+        <v>0.2295251375000001</v>
+      </c>
+      <c r="P17">
+        <v>0.6885754124999999</v>
+      </c>
+      <c r="Q17">
+        <v>1.4295754125</v>
+      </c>
+      <c r="R17">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="S17">
+        <v>0.1233549450735569</v>
+      </c>
+      <c r="T17">
+        <v>1.249658410694696</v>
+      </c>
+      <c r="U17">
+        <v>0.0457</v>
+      </c>
+      <c r="V17">
+        <v>0.2500000000000001</v>
+      </c>
+      <c r="W17">
+        <v>0.034275</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y17">
+        <v>85.23365857910261</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>0.16</v>
+      </c>
+      <c r="B18">
+        <v>0.1097610235636597</v>
+      </c>
+      <c r="C18">
+        <v>1.349361145656627</v>
+      </c>
+      <c r="D18">
+        <v>1.603761145656627</v>
+      </c>
+      <c r="E18">
+        <v>0.2544</v>
+      </c>
+      <c r="F18">
+        <v>0.2544</v>
+      </c>
+      <c r="G18">
+        <v>0</v>
+      </c>
+      <c r="H18">
+        <v>1.59</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>1.67</v>
+      </c>
+      <c r="K18">
+        <v>0.741</v>
+      </c>
+      <c r="L18">
+        <v>0.9289999999999999</v>
+      </c>
+      <c r="M18">
+        <v>0.01162608</v>
+      </c>
+      <c r="N18">
+        <v>0.91737392</v>
+      </c>
+      <c r="O18">
+        <v>0.2293434800000001</v>
+      </c>
+      <c r="P18">
+        <v>0.6880304399999999</v>
+      </c>
+      <c r="Q18">
+        <v>1.42903044</v>
+      </c>
+      <c r="R18">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="S18">
+        <v>0.1241393137662616</v>
+      </c>
+      <c r="T18">
+        <v>1.261250789272568</v>
+      </c>
+      <c r="U18">
+        <v>0.0457</v>
+      </c>
+      <c r="V18">
+        <v>0.2500000000000001</v>
+      </c>
+      <c r="W18">
+        <v>0.034275</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y18">
+        <v>79.90655491790868</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>0.17</v>
+      </c>
+      <c r="B19">
+        <v>0.109529093814796</v>
+      </c>
+      <c r="C19">
+        <v>1.334329130530452</v>
+      </c>
+      <c r="D19">
+        <v>1.604629130530452</v>
+      </c>
+      <c r="E19">
+        <v>0.2703</v>
+      </c>
+      <c r="F19">
+        <v>0.2703</v>
+      </c>
+      <c r="G19">
+        <v>0</v>
+      </c>
+      <c r="H19">
+        <v>1.59</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>1.67</v>
+      </c>
+      <c r="K19">
+        <v>0.741</v>
+      </c>
+      <c r="L19">
+        <v>0.9289999999999999</v>
+      </c>
+      <c r="M19">
+        <v>0.01235271</v>
+      </c>
+      <c r="N19">
+        <v>0.9166472899999999</v>
+      </c>
+      <c r="O19">
+        <v>0.2291618225000001</v>
+      </c>
+      <c r="P19">
+        <v>0.6874854674999998</v>
+      </c>
+      <c r="Q19">
+        <v>1.4284854675</v>
+      </c>
+      <c r="R19">
+        <v>0.2048192771084338</v>
+      </c>
+      <c r="S19">
+        <v>0.1249425829093928</v>
+      </c>
+      <c r="T19">
+        <v>1.273122502274004</v>
+      </c>
+      <c r="U19">
+        <v>0.0457</v>
+      </c>
+      <c r="V19">
+        <v>0.2500000000000001</v>
+      </c>
+      <c r="W19">
+        <v>0.034275</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y19">
+        <v>75.20616933450228</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>0.18</v>
+      </c>
+      <c r="B20">
+        <v>0.1092971640659323</v>
+      </c>
+      <c r="C20">
+        <v>1.319298055451635</v>
+      </c>
+      <c r="D20">
+        <v>1.605498055451635</v>
+      </c>
+      <c r="E20">
+        <v>0.2862</v>
+      </c>
+      <c r="F20">
+        <v>0.2862</v>
+      </c>
+      <c r="G20">
+        <v>0</v>
+      </c>
+      <c r="H20">
+        <v>1.59</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>1.67</v>
+      </c>
+      <c r="K20">
+        <v>0.741</v>
+      </c>
+      <c r="L20">
+        <v>0.9289999999999999</v>
+      </c>
+      <c r="M20">
+        <v>0.01307934</v>
+      </c>
+      <c r="N20">
+        <v>0.9159206599999999</v>
+      </c>
+      <c r="O20">
+        <v>0.2289801650000001</v>
+      </c>
+      <c r="P20">
+        <v>0.6869404949999999</v>
+      </c>
+      <c r="Q20">
+        <v>1.427940495</v>
+      </c>
+      <c r="R20">
+        <v>0.2195121951219512</v>
+      </c>
+      <c r="S20">
+        <v>0.1257654439828443</v>
+      </c>
+      <c r="T20">
+        <v>1.285283769251085</v>
+      </c>
+      <c r="U20">
+        <v>0.0457</v>
+      </c>
+      <c r="V20">
+        <v>0.2500000000000001</v>
+      </c>
+      <c r="W20">
+        <v>0.034275</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y20">
+        <v>71.02804881591884</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>0.19</v>
+      </c>
+      <c r="B21">
+        <v>0.1090652343170686</v>
+      </c>
+      <c r="C21">
+        <v>1.304267921948144</v>
+      </c>
+      <c r="D21">
+        <v>1.606367921948144</v>
+      </c>
+      <c r="E21">
+        <v>0.3021</v>
+      </c>
+      <c r="F21">
+        <v>0.3021</v>
+      </c>
+      <c r="G21">
+        <v>0</v>
+      </c>
+      <c r="H21">
+        <v>1.59</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>1.67</v>
+      </c>
+      <c r="K21">
+        <v>0.741</v>
+      </c>
+      <c r="L21">
+        <v>0.9289999999999999</v>
+      </c>
+      <c r="M21">
+        <v>0.01380597</v>
+      </c>
+      <c r="N21">
+        <v>0.9151940299999999</v>
+      </c>
+      <c r="O21">
+        <v>0.2287985075000001</v>
+      </c>
+      <c r="P21">
+        <v>0.6863955224999998</v>
+      </c>
+      <c r="Q21">
+        <v>1.4273955225</v>
+      </c>
+      <c r="R21">
+        <v>0.2345679012345679</v>
+      </c>
+      <c r="S21">
+        <v>0.126608622613665</v>
+      </c>
+      <c r="T21">
+        <v>1.297745314425131</v>
+      </c>
+      <c r="U21">
+        <v>0.0457</v>
+      </c>
+      <c r="V21">
+        <v>0.2500000000000001</v>
+      </c>
+      <c r="W21">
+        <v>0.034275</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y21">
+        <v>67.28973045718625</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>0.2</v>
+      </c>
+      <c r="B22">
+        <v>0.1088333045682049</v>
+      </c>
+      <c r="C22">
+        <v>1.289238731551257</v>
+      </c>
+      <c r="D22">
+        <v>1.607238731551258</v>
+      </c>
+      <c r="E22">
+        <v>0.3180000000000001</v>
+      </c>
+      <c r="F22">
+        <v>0.3180000000000001</v>
+      </c>
+      <c r="G22">
+        <v>0</v>
+      </c>
+      <c r="H22">
+        <v>1.59</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>1.67</v>
+      </c>
+      <c r="K22">
+        <v>0.741</v>
+      </c>
+      <c r="L22">
+        <v>0.9289999999999999</v>
+      </c>
+      <c r="M22">
+        <v>0.0145326</v>
+      </c>
+      <c r="N22">
+        <v>0.9144673999999999</v>
+      </c>
+      <c r="O22">
+        <v>0.2286168500000001</v>
+      </c>
+      <c r="P22">
+        <v>0.6858505499999998</v>
+      </c>
+      <c r="Q22">
+        <v>1.42685055</v>
+      </c>
+      <c r="R22">
+        <v>0.25</v>
+      </c>
+      <c r="S22">
+        <v>0.1274728807102561</v>
+      </c>
+      <c r="T22">
+        <v>1.310518398228528</v>
+      </c>
+      <c r="U22">
+        <v>0.0457</v>
+      </c>
+      <c r="V22">
+        <v>0.2500000000000001</v>
+      </c>
+      <c r="W22">
+        <v>0.034275</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y22">
+        <v>63.92524393432694</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>0.21</v>
+      </c>
+      <c r="B23">
+        <v>0.1086013748193412</v>
+      </c>
+      <c r="C23">
+        <v>1.274210485795578</v>
+      </c>
+      <c r="D23">
+        <v>1.608110485795578</v>
+      </c>
+      <c r="E23">
+        <v>0.3339</v>
+      </c>
+      <c r="F23">
+        <v>0.3339</v>
+      </c>
+      <c r="G23">
+        <v>0</v>
+      </c>
+      <c r="H23">
+        <v>1.59</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>1.67</v>
+      </c>
+      <c r="K23">
+        <v>0.741</v>
+      </c>
+      <c r="L23">
+        <v>0.9289999999999999</v>
+      </c>
+      <c r="M23">
+        <v>0.01525923</v>
+      </c>
+      <c r="N23">
+        <v>0.91374077</v>
+      </c>
+      <c r="O23">
+        <v>0.2284351925000001</v>
+      </c>
+      <c r="P23">
+        <v>0.6853055774999999</v>
+      </c>
+      <c r="Q23">
+        <v>1.4263055775</v>
+      </c>
+      <c r="R23">
+        <v>0.2658227848101266</v>
+      </c>
+      <c r="S23">
+        <v>0.1283590187586598</v>
+      </c>
+      <c r="T23">
+        <v>1.323614851242138</v>
+      </c>
+      <c r="U23">
+        <v>0.0457</v>
+      </c>
+      <c r="V23">
+        <v>0.2500000000000001</v>
+      </c>
+      <c r="W23">
+        <v>0.034275</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y23">
+        <v>60.881184699359</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>0.22</v>
+      </c>
+      <c r="B24">
+        <v>0.1083694450704775</v>
+      </c>
+      <c r="C24">
+        <v>1.259183186219039</v>
+      </c>
+      <c r="D24">
+        <v>1.608983186219038</v>
+      </c>
+      <c r="E24">
+        <v>0.3498</v>
+      </c>
+      <c r="F24">
+        <v>0.3498</v>
+      </c>
+      <c r="G24">
+        <v>0</v>
+      </c>
+      <c r="H24">
+        <v>1.59</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>1.67</v>
+      </c>
+      <c r="K24">
+        <v>0.741</v>
+      </c>
+      <c r="L24">
+        <v>0.9289999999999999</v>
+      </c>
+      <c r="M24">
+        <v>0.01598586</v>
+      </c>
+      <c r="N24">
+        <v>0.9130141399999999</v>
+      </c>
+      <c r="O24">
+        <v>0.2282535350000001</v>
+      </c>
+      <c r="P24">
+        <v>0.6847606049999998</v>
+      </c>
+      <c r="Q24">
+        <v>1.425760605</v>
+      </c>
+      <c r="R24">
+        <v>0.282051282051282</v>
+      </c>
+      <c r="S24">
+        <v>0.129267878295484</v>
+      </c>
+      <c r="T24">
+        <v>1.337047110743276</v>
+      </c>
+      <c r="U24">
+        <v>0.0457</v>
+      </c>
+      <c r="V24">
+        <v>0.2500000000000001</v>
+      </c>
+      <c r="W24">
+        <v>0.034275</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y24">
+        <v>58.11385812211541</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>0.23</v>
+      </c>
+      <c r="B25">
+        <v>0.1081375153216138</v>
+      </c>
+      <c r="C25">
+        <v>1.244156834362912</v>
+      </c>
+      <c r="D25">
+        <v>1.609856834362912</v>
+      </c>
+      <c r="E25">
+        <v>0.3657</v>
+      </c>
+      <c r="F25">
+        <v>0.3657</v>
+      </c>
+      <c r="G25">
+        <v>0</v>
+      </c>
+      <c r="H25">
+        <v>1.59</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>1.67</v>
+      </c>
+      <c r="K25">
+        <v>0.741</v>
+      </c>
+      <c r="L25">
+        <v>0.9289999999999999</v>
+      </c>
+      <c r="M25">
+        <v>0.01671249</v>
+      </c>
+      <c r="N25">
+        <v>0.91228751</v>
+      </c>
+      <c r="O25">
+        <v>0.2280718775000001</v>
+      </c>
+      <c r="P25">
+        <v>0.6842156324999998</v>
+      </c>
+      <c r="Q25">
+        <v>1.4252156325</v>
+      </c>
+      <c r="R25">
+        <v>0.2987012987012987</v>
+      </c>
+      <c r="S25">
+        <v>0.1302003445735245</v>
+      </c>
+      <c r="T25">
+        <v>1.350828260101586</v>
+      </c>
+      <c r="U25">
+        <v>0.0457</v>
+      </c>
+      <c r="V25">
+        <v>0.2500000000000001</v>
+      </c>
+      <c r="W25">
+        <v>0.034275</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y25">
+        <v>55.58716863854517</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>0.24</v>
+      </c>
+      <c r="B26">
+        <v>0.1079055855727502</v>
+      </c>
+      <c r="C26">
+        <v>1.229131431771822</v>
+      </c>
+      <c r="D26">
+        <v>1.610731431771822</v>
+      </c>
+      <c r="E26">
+        <v>0.3816</v>
+      </c>
+      <c r="F26">
+        <v>0.3816</v>
+      </c>
+      <c r="G26">
+        <v>0</v>
+      </c>
+      <c r="H26">
+        <v>1.59</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>1.67</v>
+      </c>
+      <c r="K26">
+        <v>0.741</v>
+      </c>
+      <c r="L26">
+        <v>0.9289999999999999</v>
+      </c>
+      <c r="M26">
+        <v>0.01743912</v>
+      </c>
+      <c r="N26">
+        <v>0.9115608799999999</v>
+      </c>
+      <c r="O26">
+        <v>0.2278902200000001</v>
+      </c>
+      <c r="P26">
+        <v>0.6836706599999998</v>
+      </c>
+      <c r="Q26">
+        <v>1.42467066</v>
+      </c>
+      <c r="R26">
+        <v>0.3157894736842105</v>
+      </c>
+      <c r="S26">
+        <v>0.1311573494378291</v>
+      </c>
+      <c r="T26">
+        <v>1.364972071285115</v>
+      </c>
+      <c r="U26">
+        <v>0.0457</v>
+      </c>
+      <c r="V26">
+        <v>0.2500000000000001</v>
+      </c>
+      <c r="W26">
+        <v>0.034275</v>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y26">
+        <v>53.27103661193912</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>0.25</v>
+      </c>
+      <c r="B27">
+        <v>0.1076736558238865</v>
+      </c>
+      <c r="C27">
+        <v>1.214106979993749</v>
+      </c>
+      <c r="D27">
+        <v>1.611606979993749</v>
+      </c>
+      <c r="E27">
+        <v>0.3975</v>
+      </c>
+      <c r="F27">
+        <v>0.3975</v>
+      </c>
+      <c r="G27">
+        <v>0</v>
+      </c>
+      <c r="H27">
+        <v>1.59</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>1.67</v>
+      </c>
+      <c r="K27">
+        <v>0.741</v>
+      </c>
+      <c r="L27">
+        <v>0.9289999999999999</v>
+      </c>
+      <c r="M27">
+        <v>0.01816575</v>
+      </c>
+      <c r="N27">
+        <v>0.91083425</v>
+      </c>
+      <c r="O27">
+        <v>0.2277085625000001</v>
+      </c>
+      <c r="P27">
+        <v>0.6831256874999998</v>
+      </c>
+      <c r="Q27">
+        <v>1.4241256875</v>
+      </c>
+      <c r="R27">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="S27">
+        <v>0.1321398744318486</v>
+      </c>
+      <c r="T27">
+        <v>1.379493050766872</v>
+      </c>
+      <c r="U27">
+        <v>0.0457</v>
+      </c>
+      <c r="V27">
+        <v>0.2500000000000001</v>
+      </c>
+      <c r="W27">
+        <v>0.034275</v>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y27">
+        <v>51.14019514746156</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>0.26</v>
+      </c>
+      <c r="B28">
+        <v>0.1074417260750228</v>
+      </c>
+      <c r="C28">
+        <v>1.199083480580042</v>
+      </c>
+      <c r="D28">
+        <v>1.612483480580042</v>
+      </c>
+      <c r="E28">
+        <v>0.4134</v>
+      </c>
+      <c r="F28">
+        <v>0.4134</v>
+      </c>
+      <c r="G28">
+        <v>0</v>
+      </c>
+      <c r="H28">
+        <v>1.59</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>1.67</v>
+      </c>
+      <c r="K28">
+        <v>0.741</v>
+      </c>
+      <c r="L28">
+        <v>0.9289999999999999</v>
+      </c>
+      <c r="M28">
+        <v>0.01889238</v>
+      </c>
+      <c r="N28">
+        <v>0.9101076199999999</v>
+      </c>
+      <c r="O28">
+        <v>0.2275269050000001</v>
+      </c>
+      <c r="P28">
+        <v>0.6825807149999998</v>
+      </c>
+      <c r="Q28">
+        <v>1.423580715</v>
+      </c>
+      <c r="R28">
+        <v>0.3513513513513514</v>
+      </c>
+      <c r="S28">
+        <v>0.1331489541554361</v>
+      </c>
+      <c r="T28">
+        <v>1.394406489153541</v>
+      </c>
+      <c r="U28">
+        <v>0.0457</v>
+      </c>
+      <c r="V28">
+        <v>0.2500000000000001</v>
+      </c>
+      <c r="W28">
+        <v>0.034275</v>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y28">
+        <v>49.17326456486688</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>0.27</v>
+      </c>
+      <c r="B29">
+        <v>0.107209796326159</v>
+      </c>
+      <c r="C29">
+        <v>1.184060935085426</v>
+      </c>
+      <c r="D29">
+        <v>1.613360935085426</v>
+      </c>
+      <c r="E29">
+        <v>0.4293000000000001</v>
+      </c>
+      <c r="F29">
+        <v>0.4293000000000001</v>
+      </c>
+      <c r="G29">
+        <v>0</v>
+      </c>
+      <c r="H29">
+        <v>1.59</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>1.67</v>
+      </c>
+      <c r="K29">
+        <v>0.741</v>
+      </c>
+      <c r="L29">
+        <v>0.9289999999999999</v>
+      </c>
+      <c r="M29">
+        <v>0.01961901000000001</v>
+      </c>
+      <c r="N29">
+        <v>0.9093809899999999</v>
+      </c>
+      <c r="O29">
+        <v>0.2273452475000001</v>
+      </c>
+      <c r="P29">
+        <v>0.6820357424999999</v>
+      </c>
+      <c r="Q29">
+        <v>1.4230357425</v>
+      </c>
+      <c r="R29">
+        <v>0.3698630136986302</v>
+      </c>
+      <c r="S29">
+        <v>0.134185679898848</v>
+      </c>
+      <c r="T29">
+        <v>1.409728514893269</v>
+      </c>
+      <c r="U29">
+        <v>0.0457</v>
+      </c>
+      <c r="V29">
+        <v>0.2500000000000001</v>
+      </c>
+      <c r="W29">
+        <v>0.034275</v>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y29">
+        <v>47.35203254394588</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>0.28</v>
+      </c>
+      <c r="B30">
+        <v>0.1069778665772954</v>
+      </c>
+      <c r="C30">
+        <v>1.169039345068013</v>
+      </c>
+      <c r="D30">
+        <v>1.614239345068013</v>
+      </c>
+      <c r="E30">
+        <v>0.4452</v>
+      </c>
+      <c r="F30">
+        <v>0.4452</v>
+      </c>
+      <c r="G30">
+        <v>0</v>
+      </c>
+      <c r="H30">
+        <v>1.59</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>1.67</v>
+      </c>
+      <c r="K30">
+        <v>0.741</v>
+      </c>
+      <c r="L30">
+        <v>0.9289999999999999</v>
+      </c>
+      <c r="M30">
+        <v>0.02034564000000001</v>
+      </c>
+      <c r="N30">
+        <v>0.9086543599999999</v>
+      </c>
+      <c r="O30">
+        <v>0.2271635900000001</v>
+      </c>
+      <c r="P30">
+        <v>0.6814907699999998</v>
+      </c>
+      <c r="Q30">
+        <v>1.42249077</v>
+      </c>
+      <c r="R30">
+        <v>0.388888888888889</v>
+      </c>
+      <c r="S30">
+        <v>0.1352512035795769</v>
+      </c>
+      <c r="T30">
+        <v>1.425476152459101</v>
+      </c>
+      <c r="U30">
+        <v>0.0457</v>
+      </c>
+      <c r="V30">
+        <v>0.2500000000000001</v>
+      </c>
+      <c r="W30">
+        <v>0.034275</v>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y30">
+        <v>45.66088852451924</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>0.29</v>
+      </c>
+      <c r="B31">
+        <v>0.1067459368284317</v>
+      </c>
+      <c r="C31">
+        <v>1.15401871208931</v>
+      </c>
+      <c r="D31">
+        <v>1.61511871208931</v>
+      </c>
+      <c r="E31">
+        <v>0.4611</v>
+      </c>
+      <c r="F31">
+        <v>0.4611</v>
+      </c>
+      <c r="G31">
+        <v>0</v>
+      </c>
+      <c r="H31">
+        <v>1.59</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>1.67</v>
+      </c>
+      <c r="K31">
+        <v>0.741</v>
+      </c>
+      <c r="L31">
+        <v>0.9289999999999999</v>
+      </c>
+      <c r="M31">
+        <v>0.02107227</v>
+      </c>
+      <c r="N31">
+        <v>0.9079277299999999</v>
+      </c>
+      <c r="O31">
+        <v>0.2269819325000001</v>
+      </c>
+      <c r="P31">
+        <v>0.6809457974999998</v>
+      </c>
+      <c r="Q31">
+        <v>1.4219457975</v>
+      </c>
+      <c r="R31">
+        <v>0.4084507042253521</v>
+      </c>
+      <c r="S31">
+        <v>0.1363467420118756</v>
+      </c>
+      <c r="T31">
+        <v>1.441667385449322</v>
+      </c>
+      <c r="U31">
+        <v>0.0457</v>
+      </c>
+      <c r="V31">
+        <v>0.2500000000000001</v>
+      </c>
+      <c r="W31">
+        <v>0.034275</v>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y31">
+        <v>44.08637512712203</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>0.3</v>
+      </c>
+      <c r="B32">
+        <v>0.1065140070795679</v>
+      </c>
+      <c r="C32">
+        <v>1.138999037714228</v>
+      </c>
+      <c r="D32">
+        <v>1.615999037714228</v>
+      </c>
+      <c r="E32">
+        <v>0.477</v>
+      </c>
+      <c r="F32">
+        <v>0.477</v>
+      </c>
+      <c r="G32">
+        <v>0</v>
+      </c>
+      <c r="H32">
+        <v>1.59</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>1.67</v>
+      </c>
+      <c r="K32">
+        <v>0.741</v>
+      </c>
+      <c r="L32">
+        <v>0.9289999999999999</v>
+      </c>
+      <c r="M32">
+        <v>0.0217989</v>
+      </c>
+      <c r="N32">
+        <v>0.9072011</v>
+      </c>
+      <c r="O32">
+        <v>0.2268002750000001</v>
+      </c>
+      <c r="P32">
+        <v>0.6804008249999999</v>
+      </c>
+      <c r="Q32">
+        <v>1.421400825</v>
+      </c>
+      <c r="R32">
+        <v>0.4285714285714286</v>
+      </c>
+      <c r="S32">
+        <v>0.1374735815422399</v>
+      </c>
+      <c r="T32">
+        <v>1.458321225096407</v>
+      </c>
+      <c r="U32">
+        <v>0.0457</v>
+      </c>
+      <c r="V32">
+        <v>0.2500000000000001</v>
+      </c>
+      <c r="W32">
+        <v>0.034275</v>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y32">
+        <v>42.6168292895513</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>0.31</v>
+      </c>
+      <c r="B33">
+        <v>0.1062820773307042</v>
+      </c>
+      <c r="C33">
+        <v>1.123980323511091</v>
+      </c>
+      <c r="D33">
+        <v>1.616880323511091</v>
+      </c>
+      <c r="E33">
+        <v>0.4929</v>
+      </c>
+      <c r="F33">
+        <v>0.4929</v>
+      </c>
+      <c r="G33">
+        <v>0</v>
+      </c>
+      <c r="H33">
+        <v>1.59</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>1.67</v>
+      </c>
+      <c r="K33">
+        <v>0.741</v>
+      </c>
+      <c r="L33">
+        <v>0.9289999999999999</v>
+      </c>
+      <c r="M33">
+        <v>0.02252553</v>
+      </c>
+      <c r="N33">
+        <v>0.9064744699999999</v>
+      </c>
+      <c r="O33">
+        <v>0.2266186175000001</v>
+      </c>
+      <c r="P33">
+        <v>0.6798558524999998</v>
+      </c>
+      <c r="Q33">
+        <v>1.4208558525</v>
+      </c>
+      <c r="R33">
+        <v>0.4492753623188406</v>
+      </c>
+      <c r="S33">
+        <v>0.1386330830879772</v>
+      </c>
+      <c r="T33">
+        <v>1.475457784733263</v>
+      </c>
+      <c r="U33">
+        <v>0.0457</v>
+      </c>
+      <c r="V33">
+        <v>0.2500000000000001</v>
+      </c>
+      <c r="W33">
+        <v>0.034275</v>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y33">
+        <v>41.2420928608561</v>
+      </c>
+      <c r="Z33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>0.32</v>
+      </c>
+      <c r="B34">
+        <v>0.1060501475818406</v>
+      </c>
+      <c r="C34">
+        <v>1.108962571051646</v>
+      </c>
+      <c r="D34">
+        <v>1.617762571051647</v>
+      </c>
+      <c r="E34">
+        <v>0.5088</v>
+      </c>
+      <c r="F34">
+        <v>0.5088</v>
+      </c>
+      <c r="G34">
+        <v>0</v>
+      </c>
+      <c r="H34">
+        <v>1.59</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>1.67</v>
+      </c>
+      <c r="K34">
+        <v>0.741</v>
+      </c>
+      <c r="L34">
+        <v>0.9289999999999999</v>
+      </c>
+      <c r="M34">
+        <v>0.02325216</v>
+      </c>
+      <c r="N34">
+        <v>0.90574784</v>
+      </c>
+      <c r="O34">
+        <v>0.2264369600000001</v>
+      </c>
+      <c r="P34">
+        <v>0.6793108799999998</v>
+      </c>
+      <c r="Q34">
+        <v>1.42031088</v>
+      </c>
+      <c r="R34">
+        <v>0.4705882352941177</v>
+      </c>
+      <c r="S34">
+        <v>0.1398266876203538</v>
+      </c>
+      <c r="T34">
+        <v>1.493098360830026</v>
+      </c>
+      <c r="U34">
+        <v>0.0457</v>
+      </c>
+      <c r="V34">
+        <v>0.2500000000000001</v>
+      </c>
+      <c r="W34">
+        <v>0.034275</v>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y34">
+        <v>39.95327745895434</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>0.33</v>
+      </c>
+      <c r="B35">
+        <v>0.1058182178329768</v>
+      </c>
+      <c r="C35">
+        <v>1.093945781911076</v>
+      </c>
+      <c r="D35">
+        <v>1.618645781911076</v>
+      </c>
+      <c r="E35">
+        <v>0.5247000000000001</v>
+      </c>
+      <c r="F35">
+        <v>0.5247000000000001</v>
+      </c>
+      <c r="G35">
+        <v>0</v>
+      </c>
+      <c r="H35">
+        <v>1.59</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>1.67</v>
+      </c>
+      <c r="K35">
+        <v>0.741</v>
+      </c>
+      <c r="L35">
+        <v>0.9289999999999999</v>
+      </c>
+      <c r="M35">
+        <v>0.02397879</v>
+      </c>
+      <c r="N35">
+        <v>0.9050212099999999</v>
+      </c>
+      <c r="O35">
+        <v>0.2262553025000001</v>
+      </c>
+      <c r="P35">
+        <v>0.6787659074999999</v>
+      </c>
+      <c r="Q35">
+        <v>1.4197659075</v>
+      </c>
+      <c r="R35">
+        <v>0.4925373134328359</v>
+      </c>
+      <c r="S35">
+        <v>0.1410559221387714</v>
+      </c>
+      <c r="T35">
+        <v>1.511265521287886</v>
+      </c>
+      <c r="U35">
+        <v>0.0457</v>
+      </c>
+      <c r="V35">
+        <v>0.2500000000000001</v>
+      </c>
+      <c r="W35">
+        <v>0.034275</v>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y35">
+        <v>38.74257208141027</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>0.34</v>
+      </c>
+      <c r="B36">
+        <v>0.1055862880841131</v>
+      </c>
+      <c r="C36">
+        <v>1.078929957668</v>
+      </c>
+      <c r="D36">
+        <v>1.619529957668</v>
+      </c>
+      <c r="E36">
+        <v>0.5406000000000001</v>
+      </c>
+      <c r="F36">
+        <v>0.5406000000000001</v>
+      </c>
+      <c r="G36">
+        <v>0</v>
+      </c>
+      <c r="H36">
+        <v>1.59</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>1.67</v>
+      </c>
+      <c r="K36">
+        <v>0.741</v>
+      </c>
+      <c r="L36">
+        <v>0.9289999999999999</v>
+      </c>
+      <c r="M36">
+        <v>0.02470542000000001</v>
+      </c>
+      <c r="N36">
+        <v>0.90429458</v>
+      </c>
+      <c r="O36">
+        <v>0.2260736450000001</v>
+      </c>
+      <c r="P36">
+        <v>0.6782209349999999</v>
+      </c>
+      <c r="Q36">
+        <v>1.419220935</v>
+      </c>
+      <c r="R36">
+        <v>0.5151515151515152</v>
+      </c>
+      <c r="S36">
+        <v>0.1423224061880503</v>
+      </c>
+      <c r="T36">
+        <v>1.529983201759621</v>
+      </c>
+      <c r="U36">
+        <v>0.0457</v>
+      </c>
+      <c r="V36">
+        <v>0.2500000000000001</v>
+      </c>
+      <c r="W36">
+        <v>0.034275</v>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y36">
+        <v>37.60308466725115</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>0.35</v>
+      </c>
+      <c r="B37">
+        <v>0.1053543583352494</v>
+      </c>
+      <c r="C37">
+        <v>1.063915099904492</v>
+      </c>
+      <c r="D37">
+        <v>1.620415099904492</v>
+      </c>
+      <c r="E37">
+        <v>0.5565000000000001</v>
+      </c>
+      <c r="F37">
+        <v>0.5565000000000001</v>
+      </c>
+      <c r="G37">
+        <v>0</v>
+      </c>
+      <c r="H37">
+        <v>1.59</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>1.67</v>
+      </c>
+      <c r="K37">
+        <v>0.741</v>
+      </c>
+      <c r="L37">
+        <v>0.9289999999999999</v>
+      </c>
+      <c r="M37">
+        <v>0.02543205000000001</v>
+      </c>
+      <c r="N37">
+        <v>0.9035679499999999</v>
+      </c>
+      <c r="O37">
+        <v>0.2258919875000001</v>
+      </c>
+      <c r="P37">
+        <v>0.6776759624999998</v>
+      </c>
+      <c r="Q37">
+        <v>1.4186759625</v>
+      </c>
+      <c r="R37">
+        <v>0.5384615384615385</v>
+      </c>
+      <c r="S37">
+        <v>0.1436278589773068</v>
+      </c>
+      <c r="T37">
+        <v>1.549276810861256</v>
+      </c>
+      <c r="U37">
+        <v>0.0457</v>
+      </c>
+      <c r="V37">
+        <v>0.2500000000000001</v>
+      </c>
+      <c r="W37">
+        <v>0.034275</v>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y37">
+        <v>36.52871081961539</v>
+      </c>
+      <c r="Z37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>0.36</v>
+      </c>
+      <c r="B38">
+        <v>0.1051224285863858</v>
+      </c>
+      <c r="C38">
+        <v>1.048901210206086</v>
+      </c>
+      <c r="D38">
+        <v>1.621301210206086</v>
+      </c>
+      <c r="E38">
+        <v>0.5724</v>
+      </c>
+      <c r="F38">
+        <v>0.5724</v>
+      </c>
+      <c r="G38">
+        <v>0</v>
+      </c>
+      <c r="H38">
+        <v>1.59</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>1.67</v>
+      </c>
+      <c r="K38">
+        <v>0.741</v>
+      </c>
+      <c r="L38">
+        <v>0.9289999999999999</v>
+      </c>
+      <c r="M38">
+        <v>0.02615868</v>
+      </c>
+      <c r="N38">
+        <v>0.9028413199999999</v>
+      </c>
+      <c r="O38">
+        <v>0.2257103300000001</v>
+      </c>
+      <c r="P38">
+        <v>0.6771309899999999</v>
+      </c>
+      <c r="Q38">
+        <v>1.41813099</v>
+      </c>
+      <c r="R38">
+        <v>0.5625</v>
+      </c>
+      <c r="S38">
+        <v>0.1449741071662278</v>
+      </c>
+      <c r="T38">
+        <v>1.569173345247317</v>
+      </c>
+      <c r="U38">
+        <v>0.0457</v>
+      </c>
+      <c r="V38">
+        <v>0.2500000000000001</v>
+      </c>
+      <c r="W38">
+        <v>0.034275</v>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y38">
+        <v>35.51402440795942</v>
+      </c>
+      <c r="Z38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>0.37</v>
+      </c>
+      <c r="B39">
+        <v>0.1048904988375221</v>
+      </c>
+      <c r="C39">
+        <v>1.033888290161785</v>
+      </c>
+      <c r="D39">
+        <v>1.622188290161785</v>
+      </c>
+      <c r="E39">
+        <v>0.5883</v>
+      </c>
+      <c r="F39">
+        <v>0.5883</v>
+      </c>
+      <c r="G39">
+        <v>0</v>
+      </c>
+      <c r="H39">
+        <v>1.59</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>1.67</v>
+      </c>
+      <c r="K39">
+        <v>0.741</v>
+      </c>
+      <c r="L39">
+        <v>0.9289999999999999</v>
+      </c>
+      <c r="M39">
+        <v>0.02688531000000001</v>
+      </c>
+      <c r="N39">
+        <v>0.9021146899999999</v>
+      </c>
+      <c r="O39">
+        <v>0.2255286725000001</v>
+      </c>
+      <c r="P39">
+        <v>0.6765860174999998</v>
+      </c>
+      <c r="Q39">
+        <v>1.4175860175</v>
+      </c>
+      <c r="R39">
+        <v>0.5873015873015873</v>
+      </c>
+      <c r="S39">
+        <v>0.1463630933928922</v>
+      </c>
+      <c r="T39">
+        <v>1.589701515645633</v>
+      </c>
+      <c r="U39">
+        <v>0.0457</v>
+      </c>
+      <c r="V39">
+        <v>0.2500000000000001</v>
+      </c>
+      <c r="W39">
+        <v>0.034275</v>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y39">
+        <v>34.554185910447</v>
+      </c>
+      <c r="Z39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>0.38</v>
+      </c>
+      <c r="B40">
+        <v>0.1046585690886584</v>
+      </c>
+      <c r="C40">
+        <v>1.018876341364072</v>
+      </c>
+      <c r="D40">
+        <v>1.623076341364072</v>
+      </c>
+      <c r="E40">
+        <v>0.6042000000000001</v>
+      </c>
+      <c r="F40">
+        <v>0.6042000000000001</v>
+      </c>
+      <c r="G40">
+        <v>0</v>
+      </c>
+      <c r="H40">
+        <v>1.59</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>1.67</v>
+      </c>
+      <c r="K40">
+        <v>0.741</v>
+      </c>
+      <c r="L40">
+        <v>0.9289999999999999</v>
+      </c>
+      <c r="M40">
+        <v>0.02761194</v>
+      </c>
+      <c r="N40">
+        <v>0.9013880599999999</v>
+      </c>
+      <c r="O40">
+        <v>0.2253470150000001</v>
+      </c>
+      <c r="P40">
+        <v>0.6760410449999998</v>
+      </c>
+      <c r="Q40">
+        <v>1.417041045</v>
+      </c>
+      <c r="R40">
+        <v>0.6129032258064516</v>
+      </c>
+      <c r="S40">
+        <v>0.1477968856268683</v>
+      </c>
+      <c r="T40">
+        <v>1.610891885089057</v>
+      </c>
+      <c r="U40">
+        <v>0.0457</v>
+      </c>
+      <c r="V40">
+        <v>0.2500000000000001</v>
+      </c>
+      <c r="W40">
+        <v>0.034275</v>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y40">
+        <v>33.64486522859313</v>
+      </c>
+      <c r="Z40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>0.39</v>
+      </c>
+      <c r="B41">
+        <v>0.1044266393397947</v>
+      </c>
+      <c r="C41">
+        <v>1.00386536540892</v>
+      </c>
+      <c r="D41">
+        <v>1.62396536540892</v>
+      </c>
+      <c r="E41">
+        <v>0.6201000000000001</v>
+      </c>
+      <c r="F41">
+        <v>0.6201000000000001</v>
+      </c>
+      <c r="G41">
+        <v>0</v>
+      </c>
+      <c r="H41">
+        <v>1.59</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>1.67</v>
+      </c>
+      <c r="K41">
+        <v>0.741</v>
+      </c>
+      <c r="L41">
+        <v>0.9289999999999999</v>
+      </c>
+      <c r="M41">
+        <v>0.02833857000000001</v>
+      </c>
+      <c r="N41">
+        <v>0.90066143</v>
+      </c>
+      <c r="O41">
+        <v>0.2251653575000001</v>
+      </c>
+      <c r="P41">
+        <v>0.6754960724999999</v>
+      </c>
+      <c r="Q41">
+        <v>1.4164960725</v>
+      </c>
+      <c r="R41">
+        <v>0.639344262295082</v>
+      </c>
+      <c r="S41">
+        <v>0.1492776874422864</v>
+      </c>
+      <c r="T41">
+        <v>1.63277702074374</v>
+      </c>
+      <c r="U41">
+        <v>0.0457</v>
+      </c>
+      <c r="V41">
+        <v>0.2500000000000001</v>
+      </c>
+      <c r="W41">
+        <v>0.034275</v>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y41">
+        <v>32.78217637657792</v>
+      </c>
+      <c r="Z41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>0.4</v>
+      </c>
+      <c r="B42">
+        <v>0.104194709590931</v>
+      </c>
+      <c r="C42">
+        <v>0.9888553638957986</v>
+      </c>
+      <c r="D42">
+        <v>1.624855363895799</v>
+      </c>
+      <c r="E42">
+        <v>0.6360000000000001</v>
+      </c>
+      <c r="F42">
+        <v>0.6360000000000001</v>
+      </c>
+      <c r="G42">
+        <v>0</v>
+      </c>
+      <c r="H42">
+        <v>1.59</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>1.67</v>
+      </c>
+      <c r="K42">
+        <v>0.741</v>
+      </c>
+      <c r="L42">
+        <v>0.9289999999999999</v>
+      </c>
+      <c r="M42">
+        <v>0.02906520000000001</v>
+      </c>
+      <c r="N42">
+        <v>0.8999347999999999</v>
+      </c>
+      <c r="O42">
+        <v>0.2249837000000001</v>
+      </c>
+      <c r="P42">
+        <v>0.6749510999999998</v>
+      </c>
+      <c r="Q42">
+        <v>1.4159511</v>
+      </c>
+      <c r="R42">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="S42">
+        <v>0.1508078493182183</v>
+      </c>
+      <c r="T42">
+        <v>1.655391660920246</v>
+      </c>
+      <c r="U42">
+        <v>0.0457</v>
+      </c>
+      <c r="V42">
+        <v>0.2500000000000001</v>
+      </c>
+      <c r="W42">
+        <v>0.034275</v>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y42">
+        <v>31.96262196716347</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>0.41</v>
+      </c>
+      <c r="B43">
+        <v>0.1039627798420673</v>
+      </c>
+      <c r="C43">
+        <v>0.973846338427688</v>
+      </c>
+      <c r="D43">
+        <v>1.625746338427688</v>
+      </c>
+      <c r="E43">
+        <v>0.6519</v>
+      </c>
+      <c r="F43">
+        <v>0.6519</v>
+      </c>
+      <c r="G43">
+        <v>0</v>
+      </c>
+      <c r="H43">
+        <v>1.59</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>1.67</v>
+      </c>
+      <c r="K43">
+        <v>0.741</v>
+      </c>
+      <c r="L43">
+        <v>0.9289999999999999</v>
+      </c>
+      <c r="M43">
+        <v>0.02979183000000001</v>
+      </c>
+      <c r="N43">
+        <v>0.89920817</v>
+      </c>
+      <c r="O43">
+        <v>0.2248020425000001</v>
+      </c>
+      <c r="P43">
+        <v>0.6744061274999998</v>
+      </c>
+      <c r="Q43">
+        <v>1.4154061275</v>
+      </c>
+      <c r="R43">
+        <v>0.6949152542372882</v>
+      </c>
+      <c r="S43">
+        <v>0.1523898810882496</v>
+      </c>
+      <c r="T43">
+        <v>1.678772899068837</v>
+      </c>
+      <c r="U43">
+        <v>0.0457</v>
+      </c>
+      <c r="V43">
+        <v>0.2500000000000001</v>
+      </c>
+      <c r="W43">
+        <v>0.034275</v>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y43">
+        <v>31.1830458216229</v>
+      </c>
+      <c r="Z43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>0.42</v>
+      </c>
+      <c r="B44">
+        <v>0.1037308500932036</v>
+      </c>
+      <c r="C44">
+        <v>0.9588382906110843</v>
+      </c>
+      <c r="D44">
+        <v>1.626638290611084</v>
+      </c>
+      <c r="E44">
+        <v>0.6678000000000001</v>
+      </c>
+      <c r="F44">
+        <v>0.6678000000000001</v>
+      </c>
+      <c r="G44">
+        <v>0</v>
+      </c>
+      <c r="H44">
+        <v>1.59</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>1.67</v>
+      </c>
+      <c r="K44">
+        <v>0.741</v>
+      </c>
+      <c r="L44">
+        <v>0.9289999999999999</v>
+      </c>
+      <c r="M44">
+        <v>0.03051846</v>
+      </c>
+      <c r="N44">
+        <v>0.8984815399999999</v>
+      </c>
+      <c r="O44">
+        <v>0.2246203850000001</v>
+      </c>
+      <c r="P44">
+        <v>0.6738611549999998</v>
+      </c>
+      <c r="Q44">
+        <v>1.414861155</v>
+      </c>
+      <c r="R44">
+        <v>0.7241379310344827</v>
+      </c>
+      <c r="S44">
+        <v>0.1540264656779372</v>
+      </c>
+      <c r="T44">
+        <v>1.702960386808759</v>
+      </c>
+      <c r="U44">
+        <v>0.0457</v>
+      </c>
+      <c r="V44">
+        <v>0.2500000000000001</v>
+      </c>
+      <c r="W44">
+        <v>0.034275</v>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y44">
+        <v>30.4405923496795</v>
+      </c>
+      <c r="Z44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>0.43</v>
+      </c>
+      <c r="B45">
+        <v>0.1034989203443399</v>
+      </c>
+      <c r="C45">
+        <v>0.9438312220560128</v>
+      </c>
+      <c r="D45">
+        <v>1.627531222056013</v>
+      </c>
+      <c r="E45">
+        <v>0.6837</v>
+      </c>
+      <c r="F45">
+        <v>0.6837</v>
+      </c>
+      <c r="G45">
+        <v>0</v>
+      </c>
+      <c r="H45">
+        <v>1.59</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>1.67</v>
+      </c>
+      <c r="K45">
+        <v>0.741</v>
+      </c>
+      <c r="L45">
+        <v>0.9289999999999999</v>
+      </c>
+      <c r="M45">
+        <v>0.03124509</v>
+      </c>
+      <c r="N45">
+        <v>0.89775491</v>
+      </c>
+      <c r="O45">
+        <v>0.2244387275000001</v>
+      </c>
+      <c r="P45">
+        <v>0.6733161824999998</v>
+      </c>
+      <c r="Q45">
+        <v>1.4143161825</v>
+      </c>
+      <c r="R45">
+        <v>0.7543859649122806</v>
+      </c>
+      <c r="S45">
+        <v>0.1557204742883156</v>
+      </c>
+      <c r="T45">
+        <v>1.727996558329029</v>
+      </c>
+      <c r="U45">
+        <v>0.0457</v>
+      </c>
+      <c r="V45">
+        <v>0.2500000000000001</v>
+      </c>
+      <c r="W45">
+        <v>0.034275</v>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y45">
+        <v>29.73267159736137</v>
+      </c>
+      <c r="Z45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>0.44</v>
+      </c>
+      <c r="B46">
+        <v>0.1032669905954762</v>
+      </c>
+      <c r="C46">
+        <v>0.9288251343760339</v>
+      </c>
+      <c r="D46">
+        <v>1.628425134376034</v>
+      </c>
+      <c r="E46">
+        <v>0.6996</v>
+      </c>
+      <c r="F46">
+        <v>0.6996</v>
+      </c>
+      <c r="G46">
+        <v>0</v>
+      </c>
+      <c r="H46">
+        <v>1.59</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>1.67</v>
+      </c>
+      <c r="K46">
+        <v>0.741</v>
+      </c>
+      <c r="L46">
+        <v>0.9289999999999999</v>
+      </c>
+      <c r="M46">
+        <v>0.03197172</v>
+      </c>
+      <c r="N46">
+        <v>0.8970282799999999</v>
+      </c>
+      <c r="O46">
+        <v>0.2242570700000001</v>
+      </c>
+      <c r="P46">
+        <v>0.6727712099999998</v>
+      </c>
+      <c r="Q46">
+        <v>1.41377121</v>
+      </c>
+      <c r="R46">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="S46">
+        <v>0.1574749832062075</v>
+      </c>
+      <c r="T46">
+        <v>1.753926878832165</v>
+      </c>
+      <c r="U46">
+        <v>0.0457</v>
+      </c>
+      <c r="V46">
+        <v>0.2500000000000001</v>
+      </c>
+      <c r="W46">
+        <v>0.034275</v>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y46">
+        <v>29.0569290610577</v>
+      </c>
+      <c r="Z46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>0.45</v>
+      </c>
+      <c r="B47">
+        <v>0.1030350608466125</v>
+      </c>
+      <c r="C47">
+        <v>0.9138200291882568</v>
+      </c>
+      <c r="D47">
+        <v>1.629320029188257</v>
+      </c>
+      <c r="E47">
+        <v>0.7155</v>
+      </c>
+      <c r="F47">
+        <v>0.7155</v>
+      </c>
+      <c r="G47">
+        <v>0</v>
+      </c>
+      <c r="H47">
+        <v>1.59</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>1.67</v>
+      </c>
+      <c r="K47">
+        <v>0.741</v>
+      </c>
+      <c r="L47">
+        <v>0.9289999999999999</v>
+      </c>
+      <c r="M47">
+        <v>0.03269835</v>
+      </c>
+      <c r="N47">
+        <v>0.8963016499999999</v>
+      </c>
+      <c r="O47">
+        <v>0.2240754125000001</v>
+      </c>
+      <c r="P47">
+        <v>0.6722262374999999</v>
+      </c>
+      <c r="Q47">
+        <v>1.4132262375</v>
+      </c>
+      <c r="R47">
+        <v>0.8181818181818181</v>
+      </c>
+      <c r="S47">
+        <v>0.1592932924483864</v>
+      </c>
+      <c r="T47">
+        <v>1.780800120080871</v>
+      </c>
+      <c r="U47">
+        <v>0.0457</v>
+      </c>
+      <c r="V47">
+        <v>0.2500000000000001</v>
+      </c>
+      <c r="W47">
+        <v>0.034275</v>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y47">
+        <v>28.41121952636754</v>
+      </c>
+      <c r="Z47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>0.46</v>
+      </c>
+      <c r="B48">
+        <v>0.1028031310977488</v>
+      </c>
+      <c r="C48">
+        <v>0.8988159081133469</v>
+      </c>
+      <c r="D48">
+        <v>1.630215908113347</v>
+      </c>
+      <c r="E48">
+        <v>0.7314000000000001</v>
+      </c>
+      <c r="F48">
+        <v>0.7314000000000001</v>
+      </c>
+      <c r="G48">
+        <v>0</v>
+      </c>
+      <c r="H48">
+        <v>1.59</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>1.67</v>
+      </c>
+      <c r="K48">
+        <v>0.741</v>
+      </c>
+      <c r="L48">
+        <v>0.9289999999999999</v>
+      </c>
+      <c r="M48">
+        <v>0.03342498000000001</v>
+      </c>
+      <c r="N48">
+        <v>0.8955750199999999</v>
+      </c>
+      <c r="O48">
+        <v>0.2238937550000001</v>
+      </c>
+      <c r="P48">
+        <v>0.6716812649999998</v>
+      </c>
+      <c r="Q48">
+        <v>1.412681265</v>
+      </c>
+      <c r="R48">
+        <v>0.8518518518518519</v>
+      </c>
+      <c r="S48">
+        <v>0.1611789464773126</v>
+      </c>
+      <c r="T48">
+        <v>1.80866866656101</v>
+      </c>
+      <c r="U48">
+        <v>0.0457</v>
+      </c>
+      <c r="V48">
+        <v>0.2500000000000001</v>
+      </c>
+      <c r="W48">
+        <v>0.034275</v>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y48">
+        <v>27.79358431927258</v>
+      </c>
+      <c r="Z48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>0.47</v>
+      </c>
+      <c r="B49">
+        <v>0.1025712013488851</v>
+      </c>
+      <c r="C49">
+        <v>0.8838127727755352</v>
+      </c>
+      <c r="D49">
+        <v>1.631112772775535</v>
+      </c>
+      <c r="E49">
+        <v>0.7473000000000001</v>
+      </c>
+      <c r="F49">
+        <v>0.7473000000000001</v>
+      </c>
+      <c r="G49">
+        <v>0</v>
+      </c>
+      <c r="H49">
+        <v>1.59</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>1.67</v>
+      </c>
+      <c r="K49">
+        <v>0.741</v>
+      </c>
+      <c r="L49">
+        <v>0.9289999999999999</v>
+      </c>
+      <c r="M49">
+        <v>0.03415161000000001</v>
+      </c>
+      <c r="N49">
+        <v>0.8948483899999999</v>
+      </c>
+      <c r="O49">
+        <v>0.2237120975000001</v>
+      </c>
+      <c r="P49">
+        <v>0.6711362924999998</v>
+      </c>
+      <c r="Q49">
+        <v>1.4121362925</v>
+      </c>
+      <c r="R49">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="S49">
+        <v>0.1631357572620474</v>
+      </c>
+      <c r="T49">
+        <v>1.83758885630455</v>
+      </c>
+      <c r="U49">
+        <v>0.0457</v>
+      </c>
+      <c r="V49">
+        <v>0.2500000000000001</v>
+      </c>
+      <c r="W49">
+        <v>0.034275</v>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y49">
+        <v>27.20223146141572</v>
+      </c>
+      <c r="Z49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>0.48</v>
+      </c>
+      <c r="B50">
+        <v>0.1023392716000214</v>
+      </c>
+      <c r="C50">
+        <v>0.8688106248026296</v>
+      </c>
+      <c r="D50">
+        <v>1.63201062480263</v>
+      </c>
+      <c r="E50">
+        <v>0.7632</v>
+      </c>
+      <c r="F50">
+        <v>0.7632</v>
+      </c>
+      <c r="G50">
+        <v>0</v>
+      </c>
+      <c r="H50">
+        <v>1.59</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>1.67</v>
+      </c>
+      <c r="K50">
+        <v>0.741</v>
+      </c>
+      <c r="L50">
+        <v>0.9289999999999999</v>
+      </c>
+      <c r="M50">
+        <v>0.03487824</v>
+      </c>
+      <c r="N50">
+        <v>0.89412176</v>
+      </c>
+      <c r="O50">
+        <v>0.2235304400000001</v>
+      </c>
+      <c r="P50">
+        <v>0.6705913199999999</v>
+      </c>
+      <c r="Q50">
+        <v>1.41159132</v>
+      </c>
+      <c r="R50">
+        <v>0.923076923076923</v>
+      </c>
+      <c r="S50">
+        <v>0.1651678300000411</v>
+      </c>
+      <c r="T50">
+        <v>1.867621361038226</v>
+      </c>
+      <c r="U50">
+        <v>0.0457</v>
+      </c>
+      <c r="V50">
+        <v>0.2500000000000001</v>
+      </c>
+      <c r="W50">
+        <v>0.034275</v>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y50">
+        <v>26.63551830596956</v>
+      </c>
+      <c r="Z50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>0.49</v>
+      </c>
+      <c r="B51">
+        <v>0.1021073418511577</v>
+      </c>
+      <c r="C51">
+        <v>0.8538094658260241</v>
+      </c>
+      <c r="D51">
+        <v>1.632909465826024</v>
+      </c>
+      <c r="E51">
+        <v>0.7791</v>
+      </c>
+      <c r="F51">
+        <v>0.7791</v>
+      </c>
+      <c r="G51">
+        <v>0</v>
+      </c>
+      <c r="H51">
+        <v>1.59</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>1.67</v>
+      </c>
+      <c r="K51">
+        <v>0.741</v>
+      </c>
+      <c r="L51">
+        <v>0.9289999999999999</v>
+      </c>
+      <c r="M51">
+        <v>0.03560487</v>
+      </c>
+      <c r="N51">
+        <v>0.8933951299999999</v>
+      </c>
+      <c r="O51">
+        <v>0.2233487825000001</v>
+      </c>
+      <c r="P51">
+        <v>0.6700463474999998</v>
+      </c>
+      <c r="Q51">
+        <v>1.4110463475</v>
+      </c>
+      <c r="R51">
+        <v>0.9607843137254901</v>
+      </c>
+      <c r="S51">
+        <v>0.1672795918650151</v>
+      </c>
+      <c r="T51">
+        <v>1.898831611055576</v>
+      </c>
+      <c r="U51">
+        <v>0.0457</v>
+      </c>
+      <c r="V51">
+        <v>0.2500000000000001</v>
+      </c>
+      <c r="W51">
+        <v>0.034275</v>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y51">
+        <v>26.09193629972529</v>
+      </c>
+      <c r="Z51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>0.5</v>
+      </c>
+      <c r="B52">
+        <v>0.101875412102294</v>
+      </c>
+      <c r="C52">
+        <v>0.8388092974807088</v>
+      </c>
+      <c r="D52">
+        <v>1.633809297480709</v>
+      </c>
+      <c r="E52">
+        <v>0.795</v>
+      </c>
+      <c r="F52">
+        <v>0.795</v>
+      </c>
+      <c r="G52">
+        <v>0</v>
+      </c>
+      <c r="H52">
+        <v>1.59</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>1.67</v>
+      </c>
+      <c r="K52">
+        <v>0.741</v>
+      </c>
+      <c r="L52">
+        <v>0.9289999999999999</v>
+      </c>
+      <c r="M52">
+        <v>0.0363315</v>
+      </c>
+      <c r="N52">
+        <v>0.8926685</v>
+      </c>
+      <c r="O52">
+        <v>0.2231671250000001</v>
+      </c>
+      <c r="P52">
+        <v>0.6695013749999998</v>
+      </c>
+      <c r="Q52">
+        <v>1.410501375</v>
+      </c>
+      <c r="R52">
+        <v>1</v>
+      </c>
+      <c r="S52">
+        <v>0.169475824204588</v>
+      </c>
+      <c r="T52">
+        <v>1.931290271073621</v>
+      </c>
+      <c r="U52">
+        <v>0.0457</v>
+      </c>
+      <c r="V52">
+        <v>0.2500000000000001</v>
+      </c>
+      <c r="W52">
+        <v>0.034275</v>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y52">
+        <v>25.57009757373078</v>
+      </c>
+      <c r="Z52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>0.51</v>
+      </c>
+      <c r="B53">
+        <v>0.1016434823534303</v>
+      </c>
+      <c r="C53">
+        <v>0.8238101214052796</v>
+      </c>
+      <c r="D53">
+        <v>1.63471012140528</v>
+      </c>
+      <c r="E53">
+        <v>0.8109000000000001</v>
+      </c>
+      <c r="F53">
+        <v>0.8109000000000001</v>
+      </c>
+      <c r="G53">
+        <v>0</v>
+      </c>
+      <c r="H53">
+        <v>1.59</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>1.67</v>
+      </c>
+      <c r="K53">
+        <v>0.741</v>
+      </c>
+      <c r="L53">
+        <v>0.9289999999999999</v>
+      </c>
+      <c r="M53">
+        <v>0.03705813000000001</v>
+      </c>
+      <c r="N53">
+        <v>0.8919418699999999</v>
+      </c>
+      <c r="O53">
+        <v>0.2229854675000001</v>
+      </c>
+      <c r="P53">
+        <v>0.6689564024999999</v>
+      </c>
+      <c r="Q53">
+        <v>1.4099564025</v>
+      </c>
+      <c r="R53">
+        <v>1.040816326530612</v>
+      </c>
+      <c r="S53">
+        <v>0.17176169868047</v>
+      </c>
+      <c r="T53">
+        <v>1.965073774357707</v>
+      </c>
+      <c r="U53">
+        <v>0.0457</v>
+      </c>
+      <c r="V53">
+        <v>0.2500000000000001</v>
+      </c>
+      <c r="W53">
+        <v>0.034275</v>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y53">
+        <v>25.06872311150076</v>
+      </c>
+      <c r="Z53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>0.52</v>
+      </c>
+      <c r="B54">
+        <v>0.1014115526045666</v>
+      </c>
+      <c r="C54">
+        <v>0.8088119392419478</v>
+      </c>
+      <c r="D54">
+        <v>1.635611939241948</v>
+      </c>
+      <c r="E54">
+        <v>0.8268000000000001</v>
+      </c>
+      <c r="F54">
+        <v>0.8268000000000001</v>
+      </c>
+      <c r="G54">
+        <v>0</v>
+      </c>
+      <c r="H54">
+        <v>1.59</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>1.67</v>
+      </c>
+      <c r="K54">
+        <v>0.741</v>
+      </c>
+      <c r="L54">
+        <v>0.9289999999999999</v>
+      </c>
+      <c r="M54">
+        <v>0.03778476000000001</v>
+      </c>
+      <c r="N54">
+        <v>0.89121524</v>
+      </c>
+      <c r="O54">
+        <v>0.2228038100000001</v>
+      </c>
+      <c r="P54">
+        <v>0.6684114299999999</v>
+      </c>
+      <c r="Q54">
+        <v>1.40941143</v>
+      </c>
+      <c r="R54">
+        <v>1.083333333333333</v>
+      </c>
+      <c r="S54">
+        <v>0.1741428179261805</v>
+      </c>
+      <c r="T54">
+        <v>2.000264923611964</v>
+      </c>
+      <c r="U54">
+        <v>0.0457</v>
+      </c>
+      <c r="V54">
+        <v>0.2500000000000001</v>
+      </c>
+      <c r="W54">
+        <v>0.034275</v>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y54">
+        <v>24.58663228243344</v>
+      </c>
+      <c r="Z54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>0.53</v>
+      </c>
+      <c r="B55">
+        <v>0.1011796228557029</v>
+      </c>
+      <c r="C55">
+        <v>0.7938147526365512</v>
+      </c>
+      <c r="D55">
+        <v>1.636514752636551</v>
+      </c>
+      <c r="E55">
+        <v>0.8427000000000001</v>
+      </c>
+      <c r="F55">
+        <v>0.8427000000000001</v>
+      </c>
+      <c r="G55">
+        <v>0</v>
+      </c>
+      <c r="H55">
+        <v>1.59</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>1.67</v>
+      </c>
+      <c r="K55">
+        <v>0.741</v>
+      </c>
+      <c r="L55">
+        <v>0.9289999999999999</v>
+      </c>
+      <c r="M55">
+        <v>0.03851139000000001</v>
+      </c>
+      <c r="N55">
+        <v>0.8904886099999999</v>
+      </c>
+      <c r="O55">
+        <v>0.2226221525000001</v>
+      </c>
+      <c r="P55">
+        <v>0.6678664574999998</v>
+      </c>
+      <c r="Q55">
+        <v>1.4088664575</v>
+      </c>
+      <c r="R55">
+        <v>1.127659574468085</v>
+      </c>
+      <c r="S55">
+        <v>0.1766252613951126</v>
+      </c>
+      <c r="T55">
+        <v>2.036953568579168</v>
+      </c>
+      <c r="U55">
+        <v>0.0457</v>
+      </c>
+      <c r="V55">
+        <v>0.2500000000000001</v>
+      </c>
+      <c r="W55">
+        <v>0.034275</v>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y55">
+        <v>24.12273356012338</v>
+      </c>
+      <c r="Z55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>0.54</v>
+      </c>
+      <c r="B56">
+        <v>0.1009476931068392</v>
+      </c>
+      <c r="C56">
+        <v>0.778818563238563</v>
+      </c>
+      <c r="D56">
+        <v>1.637418563238563</v>
+      </c>
+      <c r="E56">
+        <v>0.8586000000000001</v>
+      </c>
+      <c r="F56">
+        <v>0.8586000000000001</v>
+      </c>
+      <c r="G56">
+        <v>0</v>
+      </c>
+      <c r="H56">
+        <v>1.59</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>1.67</v>
+      </c>
+      <c r="K56">
+        <v>0.741</v>
+      </c>
+      <c r="L56">
+        <v>0.9289999999999999</v>
+      </c>
+      <c r="M56">
+        <v>0.03923802000000001</v>
+      </c>
+      <c r="N56">
+        <v>0.88976198</v>
+      </c>
+      <c r="O56">
+        <v>0.2224404950000001</v>
+      </c>
+      <c r="P56">
+        <v>0.6673214849999999</v>
+      </c>
+      <c r="Q56">
+        <v>1.408321485</v>
+      </c>
+      <c r="R56">
+        <v>1.173913043478261</v>
+      </c>
+      <c r="S56">
+        <v>0.1792156371887809</v>
+      </c>
+      <c r="T56">
+        <v>2.075237372023207</v>
+      </c>
+      <c r="U56">
+        <v>0.0457</v>
+      </c>
+      <c r="V56">
+        <v>0.2500000000000001</v>
+      </c>
+      <c r="W56">
+        <v>0.034275</v>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y56">
+        <v>23.67601627197294</v>
+      </c>
+      <c r="Z56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>0.55</v>
+      </c>
+      <c r="B57">
+        <v>0.1007157633579755</v>
+      </c>
+      <c r="C57">
+        <v>0.7638233727011027</v>
+      </c>
+      <c r="D57">
+        <v>1.638323372701103</v>
+      </c>
+      <c r="E57">
+        <v>0.8745000000000002</v>
+      </c>
+      <c r="F57">
+        <v>0.8745000000000002</v>
+      </c>
+      <c r="G57">
+        <v>0</v>
+      </c>
+      <c r="H57">
+        <v>1.59</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>1.67</v>
+      </c>
+      <c r="K57">
+        <v>0.741</v>
+      </c>
+      <c r="L57">
+        <v>0.9289999999999999</v>
+      </c>
+      <c r="M57">
+        <v>0.03996465000000001</v>
+      </c>
+      <c r="N57">
+        <v>0.8890353499999999</v>
+      </c>
+      <c r="O57">
+        <v>0.2222588375000001</v>
+      </c>
+      <c r="P57">
+        <v>0.6667765124999998</v>
+      </c>
+      <c r="Q57">
+        <v>1.4077765125</v>
+      </c>
+      <c r="R57">
+        <v>1.222222222222223</v>
+      </c>
+      <c r="S57">
+        <v>0.1819211407955012</v>
+      </c>
+      <c r="T57">
+        <v>2.115222677842537</v>
+      </c>
+      <c r="U57">
+        <v>0.0457</v>
+      </c>
+      <c r="V57">
+        <v>0.2500000000000001</v>
+      </c>
+      <c r="W57">
+        <v>0.034275</v>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y57">
+        <v>23.24554324884616</v>
+      </c>
+      <c r="Z57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="B58">
+        <v>0.1004838336091118</v>
+      </c>
+      <c r="C58">
+        <v>0.7488291826809452</v>
+      </c>
+      <c r="D58">
+        <v>1.639229182680945</v>
+      </c>
+      <c r="E58">
+        <v>0.8904000000000001</v>
+      </c>
+      <c r="F58">
+        <v>0.8904000000000001</v>
+      </c>
+      <c r="G58">
+        <v>0</v>
+      </c>
+      <c r="H58">
+        <v>1.59</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>1.67</v>
+      </c>
+      <c r="K58">
+        <v>0.741</v>
+      </c>
+      <c r="L58">
+        <v>0.9289999999999999</v>
+      </c>
+      <c r="M58">
+        <v>0.04069128000000001</v>
+      </c>
+      <c r="N58">
+        <v>0.8883087199999999</v>
+      </c>
+      <c r="O58">
+        <v>0.2220771800000001</v>
+      </c>
+      <c r="P58">
+        <v>0.6662315399999998</v>
+      </c>
+      <c r="Q58">
+        <v>1.40723154</v>
+      </c>
+      <c r="R58">
+        <v>1.272727272727273</v>
+      </c>
+      <c r="S58">
+        <v>0.1847496218388905</v>
+      </c>
+      <c r="T58">
+        <v>2.157025497562745</v>
+      </c>
+      <c r="U58">
+        <v>0.0457</v>
+      </c>
+      <c r="V58">
+        <v>0.2500000000000001</v>
+      </c>
+      <c r="W58">
+        <v>0.034275</v>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y58">
+        <v>22.83044426225962</v>
+      </c>
+      <c r="Z58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>0.5700000000000001</v>
+      </c>
+      <c r="B59">
+        <v>0.1002519038602481</v>
+      </c>
+      <c r="C59">
+        <v>0.7338359948385313</v>
+      </c>
+      <c r="D59">
+        <v>1.640135994838531</v>
+      </c>
+      <c r="E59">
+        <v>0.9063000000000001</v>
+      </c>
+      <c r="F59">
+        <v>0.9063000000000001</v>
+      </c>
+      <c r="G59">
+        <v>0</v>
+      </c>
+      <c r="H59">
+        <v>1.59</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>1.67</v>
+      </c>
+      <c r="K59">
+        <v>0.741</v>
+      </c>
+      <c r="L59">
+        <v>0.9289999999999999</v>
+      </c>
+      <c r="M59">
+        <v>0.04141791000000001</v>
+      </c>
+      <c r="N59">
+        <v>0.8875820899999999</v>
+      </c>
+      <c r="O59">
+        <v>0.2218955225000001</v>
+      </c>
+      <c r="P59">
+        <v>0.6656865674999998</v>
+      </c>
+      <c r="Q59">
+        <v>1.4066865675</v>
+      </c>
+      <c r="R59">
+        <v>1.325581395348838</v>
+      </c>
+      <c r="S59">
+        <v>0.1877096601401119</v>
+      </c>
+      <c r="T59">
+        <v>2.200772634479242</v>
+      </c>
+      <c r="U59">
+        <v>0.0457</v>
+      </c>
+      <c r="V59">
+        <v>0.2500000000000001</v>
+      </c>
+      <c r="W59">
+        <v>0.034275</v>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y59">
+        <v>22.42991015239542</v>
+      </c>
+      <c r="Z59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>0.58</v>
+      </c>
+      <c r="B60">
+        <v>0.1000199741113844</v>
+      </c>
+      <c r="C60">
+        <v>0.7188438108379794</v>
+      </c>
+      <c r="D60">
+        <v>1.641043810837979</v>
+      </c>
+      <c r="E60">
+        <v>0.9222</v>
+      </c>
+      <c r="F60">
+        <v>0.9222</v>
+      </c>
+      <c r="G60">
+        <v>0</v>
+      </c>
+      <c r="H60">
+        <v>1.59</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>1.67</v>
+      </c>
+      <c r="K60">
+        <v>0.741</v>
+      </c>
+      <c r="L60">
+        <v>0.9289999999999999</v>
+      </c>
+      <c r="M60">
+        <v>0.04214454000000001</v>
+      </c>
+      <c r="N60">
+        <v>0.8868554599999999</v>
+      </c>
+      <c r="O60">
+        <v>0.2217138650000001</v>
+      </c>
+      <c r="P60">
+        <v>0.6651415949999998</v>
+      </c>
+      <c r="Q60">
+        <v>1.406141595</v>
+      </c>
+      <c r="R60">
+        <v>1.380952380952381</v>
+      </c>
+      <c r="S60">
+        <v>0.1908106526461534</v>
+      </c>
+      <c r="T60">
+        <v>2.246602968391763</v>
+      </c>
+      <c r="U60">
+        <v>0.0457</v>
+      </c>
+      <c r="V60">
+        <v>0.2500000000000001</v>
+      </c>
+      <c r="W60">
+        <v>0.034275</v>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y60">
+        <v>22.04318756356102</v>
+      </c>
+      <c r="Z60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>0.59</v>
+      </c>
+      <c r="B61">
+        <v>0.09978804436252074</v>
+      </c>
+      <c r="C61">
+        <v>0.7038526323470929</v>
+      </c>
+      <c r="D61">
+        <v>1.641952632347093</v>
+      </c>
+      <c r="E61">
+        <v>0.9381</v>
+      </c>
+      <c r="F61">
+        <v>0.9381</v>
+      </c>
+      <c r="G61">
+        <v>0</v>
+      </c>
+      <c r="H61">
+        <v>1.59</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>1.67</v>
+      </c>
+      <c r="K61">
+        <v>0.741</v>
+      </c>
+      <c r="L61">
+        <v>0.9289999999999999</v>
+      </c>
+      <c r="M61">
+        <v>0.04287117000000001</v>
+      </c>
+      <c r="N61">
+        <v>0.88612883</v>
+      </c>
+      <c r="O61">
+        <v>0.2215322075000001</v>
+      </c>
+      <c r="P61">
+        <v>0.6645966224999998</v>
+      </c>
+      <c r="Q61">
+        <v>1.4055966225</v>
+      </c>
+      <c r="R61">
+        <v>1.439024390243902</v>
+      </c>
+      <c r="S61">
+        <v>0.1940629130793189</v>
+      </c>
+      <c r="T61">
+        <v>2.294668928348796</v>
+      </c>
+      <c r="U61">
+        <v>0.0457</v>
+      </c>
+      <c r="V61">
+        <v>0.2500000000000001</v>
+      </c>
+      <c r="W61">
+        <v>0.034275</v>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y61">
+        <v>21.66957421502608</v>
+      </c>
+      <c r="Z61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>0.6</v>
+      </c>
+      <c r="B62">
+        <v>0.09955611461365704</v>
+      </c>
+      <c r="C62">
+        <v>0.6888624610373724</v>
+      </c>
+      <c r="D62">
+        <v>1.642862461037372</v>
+      </c>
+      <c r="E62">
+        <v>0.954</v>
+      </c>
+      <c r="F62">
+        <v>0.954</v>
+      </c>
+      <c r="G62">
+        <v>0</v>
+      </c>
+      <c r="H62">
+        <v>1.59</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>1.67</v>
+      </c>
+      <c r="K62">
+        <v>0.741</v>
+      </c>
+      <c r="L62">
+        <v>0.9289999999999999</v>
+      </c>
+      <c r="M62">
+        <v>0.0435978</v>
+      </c>
+      <c r="N62">
+        <v>0.8854021999999999</v>
+      </c>
+      <c r="O62">
+        <v>0.2213505500000001</v>
+      </c>
+      <c r="P62">
+        <v>0.6640516499999998</v>
+      </c>
+      <c r="Q62">
+        <v>1.40505165</v>
+      </c>
+      <c r="R62">
+        <v>1.5</v>
+      </c>
+      <c r="S62">
+        <v>0.1974777865341426</v>
+      </c>
+      <c r="T62">
+        <v>2.345138186303682</v>
+      </c>
+      <c r="U62">
+        <v>0.0457</v>
+      </c>
+      <c r="V62">
+        <v>0.2500000000000001</v>
+      </c>
+      <c r="W62">
+        <v>0.034275</v>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y62">
+        <v>21.30841464477565</v>
+      </c>
+      <c r="Z62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>0.61</v>
+      </c>
+      <c r="B63">
+        <v>0.09932418486479334</v>
+      </c>
+      <c r="C63">
+        <v>0.6738732985840254</v>
+      </c>
+      <c r="D63">
+        <v>1.643773298584025</v>
+      </c>
+      <c r="E63">
+        <v>0.9699</v>
+      </c>
+      <c r="F63">
+        <v>0.9699</v>
+      </c>
+      <c r="G63">
+        <v>0</v>
+      </c>
+      <c r="H63">
+        <v>1.59</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>1.67</v>
+      </c>
+      <c r="K63">
+        <v>0.741</v>
+      </c>
+      <c r="L63">
+        <v>0.9289999999999999</v>
+      </c>
+      <c r="M63">
+        <v>0.04432443</v>
+      </c>
+      <c r="N63">
+        <v>0.88467557</v>
+      </c>
+      <c r="O63">
+        <v>0.2211688925000001</v>
+      </c>
+      <c r="P63">
+        <v>0.6635066774999998</v>
+      </c>
+      <c r="Q63">
+        <v>1.4045066775</v>
+      </c>
+      <c r="R63">
+        <v>1.564102564102564</v>
+      </c>
+      <c r="S63">
+        <v>0.2010677817045983</v>
+      </c>
+      <c r="T63">
+        <v>2.398195611333177</v>
+      </c>
+      <c r="U63">
+        <v>0.0457</v>
+      </c>
+      <c r="V63">
+        <v>0.2500000000000001</v>
+      </c>
+      <c r="W63">
+        <v>0.034275</v>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y63">
+        <v>20.95909637191048</v>
+      </c>
+      <c r="Z63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>0.62</v>
+      </c>
+      <c r="B64">
+        <v>0.09909225511592964</v>
+      </c>
+      <c r="C64">
+        <v>0.658885146665976</v>
+      </c>
+      <c r="D64">
+        <v>1.644685146665976</v>
+      </c>
+      <c r="E64">
+        <v>0.9858</v>
+      </c>
+      <c r="F64">
+        <v>0.9858</v>
+      </c>
+      <c r="G64">
+        <v>0</v>
+      </c>
+      <c r="H64">
+        <v>1.59</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>1.67</v>
+      </c>
+      <c r="K64">
+        <v>0.741</v>
+      </c>
+      <c r="L64">
+        <v>0.9289999999999999</v>
+      </c>
+      <c r="M64">
+        <v>0.04505106</v>
+      </c>
+      <c r="N64">
+        <v>0.8839489399999999</v>
+      </c>
+      <c r="O64">
+        <v>0.2209872350000001</v>
+      </c>
+      <c r="P64">
+        <v>0.6629617049999998</v>
+      </c>
+      <c r="Q64">
+        <v>1.403961705</v>
+      </c>
+      <c r="R64">
+        <v>1.631578947368421</v>
+      </c>
+      <c r="S64">
+        <v>0.2048467239892885</v>
+      </c>
+      <c r="T64">
+        <v>2.454045532416856</v>
+      </c>
+      <c r="U64">
+        <v>0.0457</v>
+      </c>
+      <c r="V64">
+        <v>0.2500000000000001</v>
+      </c>
+      <c r="W64">
+        <v>0.034275</v>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y64">
+        <v>20.62104643042805</v>
+      </c>
+      <c r="Z64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>0.63</v>
+      </c>
+      <c r="B65">
+        <v>0.09886032536706593</v>
+      </c>
+      <c r="C65">
+        <v>0.6438980069658762</v>
+      </c>
+      <c r="D65">
+        <v>1.645598006965876</v>
+      </c>
+      <c r="E65">
+        <v>1.0017</v>
+      </c>
+      <c r="F65">
+        <v>1.0017</v>
+      </c>
+      <c r="G65">
+        <v>0</v>
+      </c>
+      <c r="H65">
+        <v>1.59</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>1.67</v>
+      </c>
+      <c r="K65">
+        <v>0.741</v>
+      </c>
+      <c r="L65">
+        <v>0.9289999999999999</v>
+      </c>
+      <c r="M65">
+        <v>0.04577769</v>
+      </c>
+      <c r="N65">
+        <v>0.88322231</v>
+      </c>
+      <c r="O65">
+        <v>0.2208055775000001</v>
+      </c>
+      <c r="P65">
+        <v>0.6624167324999999</v>
+      </c>
+      <c r="Q65">
+        <v>1.4034167325</v>
+      </c>
+      <c r="R65">
+        <v>1.702702702702703</v>
+      </c>
+      <c r="S65">
+        <v>0.2088299334245025</v>
+      </c>
+      <c r="T65">
+        <v>2.512914368153707</v>
+      </c>
+      <c r="U65">
+        <v>0.0457</v>
+      </c>
+      <c r="V65">
+        <v>0.2500000000000001</v>
+      </c>
+      <c r="W65">
+        <v>0.034275</v>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y65">
+        <v>20.29372823311967</v>
+      </c>
+      <c r="Z65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>0.64</v>
+      </c>
+      <c r="B66">
+        <v>0.09862839561820223</v>
+      </c>
+      <c r="C66">
+        <v>0.6289118811701158</v>
+      </c>
+      <c r="D66">
+        <v>1.646511881170116</v>
+      </c>
+      <c r="E66">
+        <v>1.0176</v>
+      </c>
+      <c r="F66">
+        <v>1.0176</v>
+      </c>
+      <c r="G66">
+        <v>0</v>
+      </c>
+      <c r="H66">
+        <v>1.59</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>1.67</v>
+      </c>
+      <c r="K66">
+        <v>0.741</v>
+      </c>
+      <c r="L66">
+        <v>0.9289999999999999</v>
+      </c>
+      <c r="M66">
+        <v>0.04650432000000001</v>
+      </c>
+      <c r="N66">
+        <v>0.8824956799999999</v>
+      </c>
+      <c r="O66">
+        <v>0.2206239200000001</v>
+      </c>
+      <c r="P66">
+        <v>0.6618717599999998</v>
+      </c>
+      <c r="Q66">
+        <v>1.40287176</v>
+      </c>
+      <c r="R66">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="S66">
+        <v>0.213034432272784</v>
+      </c>
+      <c r="T66">
+        <v>2.575053694764827</v>
+      </c>
+      <c r="U66">
+        <v>0.0457</v>
+      </c>
+      <c r="V66">
+        <v>0.2500000000000001</v>
+      </c>
+      <c r="W66">
+        <v>0.034275</v>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y66">
+        <v>19.97663872947717</v>
+      </c>
+      <c r="Z66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>0.65</v>
+      </c>
+      <c r="B67">
+        <v>0.09839646586933855</v>
+      </c>
+      <c r="C67">
+        <v>0.6139267709688327</v>
+      </c>
+      <c r="D67">
+        <v>1.647426770968833</v>
+      </c>
+      <c r="E67">
+        <v>1.0335</v>
+      </c>
+      <c r="F67">
+        <v>1.0335</v>
+      </c>
+      <c r="G67">
+        <v>0</v>
+      </c>
+      <c r="H67">
+        <v>1.59</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>1.67</v>
+      </c>
+      <c r="K67">
+        <v>0.741</v>
+      </c>
+      <c r="L67">
+        <v>0.9289999999999999</v>
+      </c>
+      <c r="M67">
+        <v>0.04723095000000001</v>
+      </c>
+      <c r="N67">
+        <v>0.8817690499999999</v>
+      </c>
+      <c r="O67">
+        <v>0.2204422625000001</v>
+      </c>
+      <c r="P67">
+        <v>0.6613267874999998</v>
+      </c>
+      <c r="Q67">
+        <v>1.4023267875</v>
+      </c>
+      <c r="R67">
+        <v>1.857142857142857</v>
+      </c>
+      <c r="S67">
+        <v>0.2174791881981102</v>
+      </c>
+      <c r="T67">
+        <v>2.64074384003944</v>
+      </c>
+      <c r="U67">
+        <v>0.0457</v>
+      </c>
+      <c r="V67">
+        <v>0.2500000000000001</v>
+      </c>
+      <c r="W67">
+        <v>0.034275</v>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y67">
+        <v>19.66930582594675</v>
+      </c>
+      <c r="Z67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>0.66</v>
+      </c>
+      <c r="B68">
+        <v>0.09816453612047485</v>
+      </c>
+      <c r="C68">
+        <v>0.5989426780559239</v>
+      </c>
+      <c r="D68">
+        <v>1.648342678055924</v>
+      </c>
+      <c r="E68">
+        <v>1.0494</v>
+      </c>
+      <c r="F68">
+        <v>1.0494</v>
+      </c>
+      <c r="G68">
+        <v>0</v>
+      </c>
+      <c r="H68">
+        <v>1.59</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>1.67</v>
+      </c>
+      <c r="K68">
+        <v>0.741</v>
+      </c>
+      <c r="L68">
+        <v>0.9289999999999999</v>
+      </c>
+      <c r="M68">
+        <v>0.04795758000000001</v>
+      </c>
+      <c r="N68">
+        <v>0.8810424199999999</v>
+      </c>
+      <c r="O68">
+        <v>0.2202606050000001</v>
+      </c>
+      <c r="P68">
+        <v>0.6607818149999998</v>
+      </c>
+      <c r="Q68">
+        <v>1.401781815</v>
+      </c>
+      <c r="R68">
+        <v>1.941176470588236</v>
+      </c>
+      <c r="S68">
+        <v>0.2221854003543378</v>
+      </c>
+      <c r="T68">
+        <v>2.710298111506678</v>
+      </c>
+      <c r="U68">
+        <v>0.0457</v>
+      </c>
+      <c r="V68">
+        <v>0.2500000000000001</v>
+      </c>
+      <c r="W68">
+        <v>0.034275</v>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y68">
+        <v>19.37128604070514</v>
+      </c>
+      <c r="Z68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>0.67</v>
+      </c>
+      <c r="B69">
+        <v>0.09793260637161115</v>
+      </c>
+      <c r="C69">
+        <v>0.5839596041290547</v>
+      </c>
+      <c r="D69">
+        <v>1.649259604129055</v>
+      </c>
+      <c r="E69">
+        <v>1.0653</v>
+      </c>
+      <c r="F69">
+        <v>1.0653</v>
+      </c>
+      <c r="G69">
+        <v>0</v>
+      </c>
+      <c r="H69">
+        <v>1.59</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>1.67</v>
+      </c>
+      <c r="K69">
+        <v>0.741</v>
+      </c>
+      <c r="L69">
+        <v>0.9289999999999999</v>
+      </c>
+      <c r="M69">
+        <v>0.04868421000000001</v>
+      </c>
+      <c r="N69">
+        <v>0.8803157899999999</v>
+      </c>
+      <c r="O69">
+        <v>0.2200789475000001</v>
+      </c>
+      <c r="P69">
+        <v>0.6602368424999998</v>
+      </c>
+      <c r="Q69">
+        <v>1.4012368425</v>
+      </c>
+      <c r="R69">
+        <v>2.030303030303031</v>
+      </c>
+      <c r="S69">
+        <v>0.2271768374897308</v>
+      </c>
+      <c r="T69">
+        <v>2.784067793365868</v>
+      </c>
+      <c r="U69">
+        <v>0.0457</v>
+      </c>
+      <c r="V69">
+        <v>0.2500000000000001</v>
+      </c>
+      <c r="W69">
+        <v>0.034275</v>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y69">
+        <v>19.0821623684558</v>
+      </c>
+      <c r="Z69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>0.68</v>
+      </c>
+      <c r="B70">
+        <v>0.09770067662274745</v>
+      </c>
+      <c r="C70">
+        <v>0.5689775508896704</v>
+      </c>
+      <c r="D70">
+        <v>1.650177550889671</v>
+      </c>
+      <c r="E70">
+        <v>1.0812</v>
+      </c>
+      <c r="F70">
+        <v>1.0812</v>
+      </c>
+      <c r="G70">
+        <v>0</v>
+      </c>
+      <c r="H70">
+        <v>1.59</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>1.67</v>
+      </c>
+      <c r="K70">
+        <v>0.741</v>
+      </c>
+      <c r="L70">
+        <v>0.9289999999999999</v>
+      </c>
+      <c r="M70">
+        <v>0.04941084000000001</v>
+      </c>
+      <c r="N70">
+        <v>0.8795891599999999</v>
+      </c>
+      <c r="O70">
+        <v>0.2198972900000001</v>
+      </c>
+      <c r="P70">
+        <v>0.6596918699999998</v>
+      </c>
+      <c r="Q70">
+        <v>1.40069187</v>
+      </c>
+      <c r="R70">
+        <v>2.125</v>
+      </c>
+      <c r="S70">
+        <v>0.2324802394460858</v>
+      </c>
+      <c r="T70">
+        <v>2.862448080341259</v>
+      </c>
+      <c r="U70">
+        <v>0.0457</v>
+      </c>
+      <c r="V70">
+        <v>0.2500000000000001</v>
+      </c>
+      <c r="W70">
+        <v>0.034275</v>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y70">
+        <v>18.80154233362557</v>
+      </c>
+      <c r="Z70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>0.6900000000000001</v>
+      </c>
+      <c r="B71">
+        <v>0.09746874687388377</v>
+      </c>
+      <c r="C71">
+        <v>0.5539965200430057</v>
+      </c>
+      <c r="D71">
+        <v>1.651096520043006</v>
+      </c>
+      <c r="E71">
+        <v>1.0971</v>
+      </c>
+      <c r="F71">
+        <v>1.0971</v>
+      </c>
+      <c r="G71">
+        <v>0</v>
+      </c>
+      <c r="H71">
+        <v>1.59</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>1.67</v>
+      </c>
+      <c r="K71">
+        <v>0.741</v>
+      </c>
+      <c r="L71">
+        <v>0.9289999999999999</v>
+      </c>
+      <c r="M71">
+        <v>0.05013747000000001</v>
+      </c>
+      <c r="N71">
+        <v>0.8788625299999999</v>
+      </c>
+      <c r="O71">
+        <v>0.2197156325000001</v>
+      </c>
+      <c r="P71">
+        <v>0.6591468974999999</v>
+      </c>
+      <c r="Q71">
+        <v>1.4001468975</v>
+      </c>
+      <c r="R71">
+        <v>2.225806451612904</v>
+      </c>
+      <c r="S71">
+        <v>0.238125796367367</v>
+      </c>
+      <c r="T71">
+        <v>2.94588516002474</v>
+      </c>
+      <c r="U71">
+        <v>0.0457</v>
+      </c>
+      <c r="V71">
+        <v>0.2500000000000001</v>
+      </c>
+      <c r="W71">
+        <v>0.034275</v>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y71">
+        <v>18.52905621284839</v>
+      </c>
+      <c r="Z71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>0.7000000000000001</v>
+      </c>
+      <c r="B72">
+        <v>0.09723681712502005</v>
+      </c>
+      <c r="C72">
+        <v>0.5390165132980973</v>
+      </c>
+      <c r="D72">
+        <v>1.652016513298098</v>
+      </c>
+      <c r="E72">
+        <v>1.113</v>
+      </c>
+      <c r="F72">
+        <v>1.113</v>
+      </c>
+      <c r="G72">
+        <v>0</v>
+      </c>
+      <c r="H72">
+        <v>1.59</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>1.67</v>
+      </c>
+      <c r="K72">
+        <v>0.741</v>
+      </c>
+      <c r="L72">
+        <v>0.9289999999999999</v>
+      </c>
+      <c r="M72">
+        <v>0.05086410000000002</v>
+      </c>
+      <c r="N72">
+        <v>0.8781359</v>
+      </c>
+      <c r="O72">
+        <v>0.2195339750000001</v>
+      </c>
+      <c r="P72">
+        <v>0.6586019249999999</v>
+      </c>
+      <c r="Q72">
+        <v>1.399601925</v>
+      </c>
+      <c r="R72">
+        <v>2.333333333333334</v>
+      </c>
+      <c r="S72">
+        <v>0.2441477237500669</v>
+      </c>
+      <c r="T72">
+        <v>3.034884711687118</v>
+      </c>
+      <c r="U72">
+        <v>0.0457</v>
+      </c>
+      <c r="V72">
+        <v>0.2500000000000001</v>
+      </c>
+      <c r="W72">
+        <v>0.034275</v>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y72">
+        <v>18.2643554098077</v>
+      </c>
+      <c r="Z72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>0.71</v>
+      </c>
+      <c r="B73">
+        <v>0.09700488737615637</v>
+      </c>
+      <c r="C73">
+        <v>0.5240375323677922</v>
+      </c>
+      <c r="D73">
+        <v>1.652937532367792</v>
+      </c>
+      <c r="E73">
+        <v>1.1289</v>
+      </c>
+      <c r="F73">
+        <v>1.1289</v>
+      </c>
+      <c r="G73">
+        <v>0</v>
+      </c>
+      <c r="H73">
+        <v>1.59</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>1.67</v>
+      </c>
+      <c r="K73">
+        <v>0.741</v>
+      </c>
+      <c r="L73">
+        <v>0.9289999999999999</v>
+      </c>
+      <c r="M73">
+        <v>0.05159073000000001</v>
+      </c>
+      <c r="N73">
+        <v>0.8774092699999999</v>
+      </c>
+      <c r="O73">
+        <v>0.2193523175000001</v>
+      </c>
+      <c r="P73">
+        <v>0.6580569524999998</v>
+      </c>
+      <c r="Q73">
+        <v>1.3990569525</v>
+      </c>
+      <c r="R73">
+        <v>2.448275862068965</v>
+      </c>
+      <c r="S73">
+        <v>0.2505849564695047</v>
+      </c>
+      <c r="T73">
+        <v>3.130022163464143</v>
+      </c>
+      <c r="U73">
+        <v>0.0457</v>
+      </c>
+      <c r="V73">
+        <v>0.2500000000000001</v>
+      </c>
+      <c r="W73">
+        <v>0.034275</v>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y73">
+        <v>18.00711096741604</v>
+      </c>
+      <c r="Z73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>0.72</v>
+      </c>
+      <c r="B74">
+        <v>0.09677295762729268</v>
+      </c>
+      <c r="C74">
+        <v>0.5090595789687589</v>
+      </c>
+      <c r="D74">
+        <v>1.653859578968759</v>
+      </c>
+      <c r="E74">
+        <v>1.1448</v>
+      </c>
+      <c r="F74">
+        <v>1.1448</v>
+      </c>
+      <c r="G74">
+        <v>0</v>
+      </c>
+      <c r="H74">
+        <v>1.59</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>1.67</v>
+      </c>
+      <c r="K74">
+        <v>0.741</v>
+      </c>
+      <c r="L74">
+        <v>0.9289999999999999</v>
+      </c>
+      <c r="M74">
+        <v>0.05231736000000001</v>
+      </c>
+      <c r="N74">
+        <v>0.87668264</v>
+      </c>
+      <c r="O74">
+        <v>0.2191706600000001</v>
+      </c>
+      <c r="P74">
+        <v>0.6575119799999999</v>
+      </c>
+      <c r="Q74">
+        <v>1.39851198</v>
+      </c>
+      <c r="R74">
+        <v>2.571428571428571</v>
+      </c>
+      <c r="S74">
+        <v>0.2574819915260452</v>
+      </c>
+      <c r="T74">
+        <v>3.231955147510956</v>
+      </c>
+      <c r="U74">
+        <v>0.0457</v>
+      </c>
+      <c r="V74">
+        <v>0.2500000000000001</v>
+      </c>
+      <c r="W74">
+        <v>0.034275</v>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y74">
+        <v>17.75701220397971</v>
+      </c>
+      <c r="Z74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>0.73</v>
+      </c>
+      <c r="B75">
+        <v>0.09654102787842896</v>
+      </c>
+      <c r="C75">
+        <v>0.4940826548214994</v>
+      </c>
+      <c r="D75">
+        <v>1.654782654821499</v>
+      </c>
+      <c r="E75">
+        <v>1.1607</v>
+      </c>
+      <c r="F75">
+        <v>1.1607</v>
+      </c>
+      <c r="G75">
+        <v>0</v>
+      </c>
+      <c r="H75">
+        <v>1.59</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>1.67</v>
+      </c>
+      <c r="K75">
+        <v>0.741</v>
+      </c>
+      <c r="L75">
+        <v>0.9289999999999999</v>
+      </c>
+      <c r="M75">
+        <v>0.05304399000000001</v>
+      </c>
+      <c r="N75">
+        <v>0.8759560099999999</v>
+      </c>
+      <c r="O75">
+        <v>0.2189890025000001</v>
+      </c>
+      <c r="P75">
+        <v>0.6569670074999998</v>
+      </c>
+      <c r="Q75">
+        <v>1.3979670075</v>
+      </c>
+      <c r="R75">
+        <v>2.703703703703703</v>
+      </c>
+      <c r="S75">
+        <v>0.2648899180682554</v>
+      </c>
+      <c r="T75">
+        <v>3.341438722968644</v>
+      </c>
+      <c r="U75">
+        <v>0.0457</v>
+      </c>
+      <c r="V75">
+        <v>0.2500000000000001</v>
+      </c>
+      <c r="W75">
+        <v>0.034275</v>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y75">
+        <v>17.51376546145944</v>
+      </c>
+      <c r="Z75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>0.74</v>
+      </c>
+      <c r="B76">
+        <v>0.09630909812956528</v>
+      </c>
+      <c r="C76">
+        <v>0.4791067616503577</v>
+      </c>
+      <c r="D76">
+        <v>1.655706761650358</v>
+      </c>
+      <c r="E76">
+        <v>1.1766</v>
+      </c>
+      <c r="F76">
+        <v>1.1766</v>
+      </c>
+      <c r="G76">
+        <v>0</v>
+      </c>
+      <c r="H76">
+        <v>1.59</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>1.67</v>
+      </c>
+      <c r="K76">
+        <v>0.741</v>
+      </c>
+      <c r="L76">
+        <v>0.9289999999999999</v>
+      </c>
+      <c r="M76">
+        <v>0.05377062000000001</v>
+      </c>
+      <c r="N76">
+        <v>0.8752293799999999</v>
+      </c>
+      <c r="O76">
+        <v>0.2188073450000001</v>
+      </c>
+      <c r="P76">
+        <v>0.6564220349999998</v>
+      </c>
+      <c r="Q76">
+        <v>1.397422035</v>
+      </c>
+      <c r="R76">
+        <v>2.846153846153846</v>
+      </c>
+      <c r="S76">
+        <v>0.2728676851137126</v>
+      </c>
+      <c r="T76">
+        <v>3.459344111923078</v>
+      </c>
+      <c r="U76">
+        <v>0.0457</v>
+      </c>
+      <c r="V76">
+        <v>0.2500000000000001</v>
+      </c>
+      <c r="W76">
+        <v>0.034275</v>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y76">
+        <v>17.2770929552235</v>
+      </c>
+      <c r="Z76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>0.75</v>
+      </c>
+      <c r="B77">
+        <v>0.09607716838070157</v>
+      </c>
+      <c r="C77">
+        <v>0.4641319011835334</v>
+      </c>
+      <c r="D77">
+        <v>1.656631901183534</v>
+      </c>
+      <c r="E77">
+        <v>1.1925</v>
+      </c>
+      <c r="F77">
+        <v>1.1925</v>
+      </c>
+      <c r="G77">
+        <v>0</v>
+      </c>
+      <c r="H77">
+        <v>1.59</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>1.67</v>
+      </c>
+      <c r="K77">
+        <v>0.741</v>
+      </c>
+      <c r="L77">
+        <v>0.9289999999999999</v>
+      </c>
+      <c r="M77">
+        <v>0.05449725000000001</v>
+      </c>
+      <c r="N77">
+        <v>0.8745027499999999</v>
+      </c>
+      <c r="O77">
+        <v>0.2186256875000001</v>
+      </c>
+      <c r="P77">
+        <v>0.6558770624999999</v>
+      </c>
+      <c r="Q77">
+        <v>1.3968770625</v>
+      </c>
+      <c r="R77">
+        <v>3</v>
+      </c>
+      <c r="S77">
+        <v>0.2814836735228063</v>
+      </c>
+      <c r="T77">
+        <v>3.586681931993866</v>
+      </c>
+      <c r="U77">
+        <v>0.0457</v>
+      </c>
+      <c r="V77">
+        <v>0.2500000000000001</v>
+      </c>
+      <c r="W77">
+        <v>0.034275</v>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y77">
+        <v>17.04673171582052</v>
+      </c>
+      <c r="Z77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>0.76</v>
+      </c>
+      <c r="B78">
+        <v>0.09584523863183789</v>
+      </c>
+      <c r="C78">
+        <v>0.4491580751530893</v>
+      </c>
+      <c r="D78">
+        <v>1.657558075153089</v>
+      </c>
+      <c r="E78">
+        <v>1.2084</v>
+      </c>
+      <c r="F78">
+        <v>1.2084</v>
+      </c>
+      <c r="G78">
+        <v>0</v>
+      </c>
+      <c r="H78">
+        <v>1.59</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>1.67</v>
+      </c>
+      <c r="K78">
+        <v>0.741</v>
+      </c>
+      <c r="L78">
+        <v>0.9289999999999999</v>
+      </c>
+      <c r="M78">
+        <v>0.05522388000000001</v>
+      </c>
+      <c r="N78">
+        <v>0.8737761199999999</v>
+      </c>
+      <c r="O78">
+        <v>0.2184440300000001</v>
+      </c>
+      <c r="P78">
+        <v>0.6553320899999999</v>
+      </c>
+      <c r="Q78">
+        <v>1.39633209</v>
+      </c>
+      <c r="R78">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="S78">
+        <v>0.2908176609659912</v>
+      </c>
+      <c r="T78">
+        <v>3.724631237070554</v>
+      </c>
+      <c r="U78">
+        <v>0.0457</v>
+      </c>
+      <c r="V78">
+        <v>0.2500000000000001</v>
+      </c>
+      <c r="W78">
+        <v>0.034275</v>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y78">
+        <v>16.82243261429657</v>
+      </c>
+      <c r="Z78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>0.77</v>
+      </c>
+      <c r="B79">
+        <v>0.09561330888297419</v>
+      </c>
+      <c r="C79">
+        <v>0.4341852852949648</v>
+      </c>
+      <c r="D79">
+        <v>1.658485285294965</v>
+      </c>
+      <c r="E79">
+        <v>1.2243</v>
+      </c>
+      <c r="F79">
+        <v>1.2243</v>
+      </c>
+      <c r="G79">
+        <v>0</v>
+      </c>
+      <c r="H79">
+        <v>1.59</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>1.67</v>
+      </c>
+      <c r="K79">
+        <v>0.741</v>
+      </c>
+      <c r="L79">
+        <v>0.9289999999999999</v>
+      </c>
+      <c r="M79">
+        <v>0.05595051000000002</v>
+      </c>
+      <c r="N79">
+        <v>0.8730494899999999</v>
+      </c>
+      <c r="O79">
+        <v>0.2182623725000001</v>
+      </c>
+      <c r="P79">
+        <v>0.6547871174999998</v>
+      </c>
+      <c r="Q79">
+        <v>1.3957871175</v>
+      </c>
+      <c r="R79">
+        <v>3.347826086956522</v>
+      </c>
+      <c r="S79">
+        <v>0.3009632994911921</v>
+      </c>
+      <c r="T79">
+        <v>3.87457613389304</v>
+      </c>
+      <c r="U79">
+        <v>0.0457</v>
+      </c>
+      <c r="V79">
+        <v>0.2500000000000001</v>
+      </c>
+      <c r="W79">
+        <v>0.034275</v>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y79">
+        <v>16.60395946346154</v>
+      </c>
+      <c r="Z79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>0.78</v>
+      </c>
+      <c r="B80">
+        <v>0.09538137913411049</v>
+      </c>
+      <c r="C80">
+        <v>0.4192135333489855</v>
+      </c>
+      <c r="D80">
+        <v>1.659413533348986</v>
+      </c>
+      <c r="E80">
+        <v>1.2402</v>
+      </c>
+      <c r="F80">
+        <v>1.2402</v>
+      </c>
+      <c r="G80">
+        <v>0</v>
+      </c>
+      <c r="H80">
+        <v>1.59</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>1.67</v>
+      </c>
+      <c r="K80">
+        <v>0.741</v>
+      </c>
+      <c r="L80">
+        <v>0.9289999999999999</v>
+      </c>
+      <c r="M80">
+        <v>0.05667714000000001</v>
+      </c>
+      <c r="N80">
+        <v>0.8723228599999999</v>
+      </c>
+      <c r="O80">
+        <v>0.2180807150000001</v>
+      </c>
+      <c r="P80">
+        <v>0.6542421449999999</v>
+      </c>
+      <c r="Q80">
+        <v>1.395242145</v>
+      </c>
+      <c r="R80">
+        <v>3.545454545454546</v>
+      </c>
+      <c r="S80">
+        <v>0.3120312687914114</v>
+      </c>
+      <c r="T80">
+        <v>4.038152384972116</v>
+      </c>
+      <c r="U80">
+        <v>0.0457</v>
+      </c>
+      <c r="V80">
+        <v>0.2500000000000001</v>
+      </c>
+      <c r="W80">
+        <v>0.034275</v>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y80">
+        <v>16.39108818828896</v>
+      </c>
+      <c r="Z80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>0.79</v>
+      </c>
+      <c r="B81">
+        <v>0.09514944938524679</v>
+      </c>
+      <c r="C81">
+        <v>0.4042428210588735</v>
+      </c>
+      <c r="D81">
+        <v>1.660342821058874</v>
+      </c>
+      <c r="E81">
+        <v>1.2561</v>
+      </c>
+      <c r="F81">
+        <v>1.2561</v>
+      </c>
+      <c r="G81">
+        <v>0</v>
+      </c>
+      <c r="H81">
+        <v>1.59</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <v>1.67</v>
+      </c>
+      <c r="K81">
+        <v>0.741</v>
+      </c>
+      <c r="L81">
+        <v>0.9289999999999999</v>
+      </c>
+      <c r="M81">
+        <v>0.05740377000000001</v>
+      </c>
+      <c r="N81">
+        <v>0.87159623</v>
+      </c>
+      <c r="O81">
+        <v>0.2178990575000001</v>
+      </c>
+      <c r="P81">
+        <v>0.6536971724999999</v>
+      </c>
+      <c r="Q81">
+        <v>1.3946971725</v>
+      </c>
+      <c r="R81">
+        <v>3.761904761904763</v>
+      </c>
+      <c r="S81">
+        <v>0.3241533304059371</v>
+      </c>
+      <c r="T81">
+        <v>4.217307326630151</v>
+      </c>
+      <c r="U81">
+        <v>0.0457</v>
+      </c>
+      <c r="V81">
+        <v>0.2500000000000001</v>
+      </c>
+      <c r="W81">
+        <v>0.034275</v>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y81">
+        <v>16.18360605932328</v>
+      </c>
+      <c r="Z81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>0.8</v>
+      </c>
+      <c r="B82">
+        <v>0.09491751963638308</v>
+      </c>
+      <c r="C82">
+        <v>0.3892731501722602</v>
+      </c>
+      <c r="D82">
+        <v>1.66127315017226</v>
+      </c>
+      <c r="E82">
+        <v>1.272</v>
+      </c>
+      <c r="F82">
+        <v>1.272</v>
+      </c>
+      <c r="G82">
+        <v>0</v>
+      </c>
+      <c r="H82">
+        <v>1.59</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>1.67</v>
+      </c>
+      <c r="K82">
+        <v>0.741</v>
+      </c>
+      <c r="L82">
+        <v>0.9289999999999999</v>
+      </c>
+      <c r="M82">
+        <v>0.05813040000000002</v>
+      </c>
+      <c r="N82">
+        <v>0.8708695999999999</v>
+      </c>
+      <c r="O82">
+        <v>0.2177174000000001</v>
+      </c>
+      <c r="P82">
+        <v>0.6531521999999998</v>
+      </c>
+      <c r="Q82">
+        <v>1.3941522</v>
+      </c>
+      <c r="R82">
+        <v>4.000000000000001</v>
+      </c>
+      <c r="S82">
+        <v>0.3374875981819155</v>
+      </c>
+      <c r="T82">
+        <v>4.41437776245399</v>
+      </c>
+      <c r="U82">
+        <v>0.0457</v>
+      </c>
+      <c r="V82">
+        <v>0.2500000000000001</v>
+      </c>
+      <c r="W82">
+        <v>0.034275</v>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y82">
+        <v>15.98131098358173</v>
+      </c>
+      <c r="Z82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="B83">
+        <v>0.09468558988751939</v>
+      </c>
+      <c r="C83">
+        <v>0.3743045224406953</v>
+      </c>
+      <c r="D83">
+        <v>1.662204522440695</v>
+      </c>
+      <c r="E83">
+        <v>1.2879</v>
+      </c>
+      <c r="F83">
+        <v>1.2879</v>
+      </c>
+      <c r="G83">
+        <v>0</v>
+      </c>
+      <c r="H83">
+        <v>1.59</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>1.67</v>
+      </c>
+      <c r="K83">
+        <v>0.741</v>
+      </c>
+      <c r="L83">
+        <v>0.9289999999999999</v>
+      </c>
+      <c r="M83">
+        <v>0.05885703</v>
+      </c>
+      <c r="N83">
+        <v>0.87014297</v>
+      </c>
+      <c r="O83">
+        <v>0.2175357425000001</v>
+      </c>
+      <c r="P83">
+        <v>0.6526072274999999</v>
+      </c>
+      <c r="Q83">
+        <v>1.3936072275</v>
+      </c>
+      <c r="R83">
+        <v>4.263157894736843</v>
+      </c>
+      <c r="S83">
+        <v>0.3522254730922074</v>
+      </c>
+      <c r="T83">
+        <v>4.632192454680339</v>
+      </c>
+      <c r="U83">
+        <v>0.0457</v>
+      </c>
+      <c r="V83">
+        <v>0.2500000000000001</v>
+      </c>
+      <c r="W83">
+        <v>0.034275</v>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y83">
+        <v>15.78401084798196</v>
+      </c>
+      <c r="Z83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="B84">
+        <v>0.09445366013865571</v>
+      </c>
+      <c r="C84">
+        <v>0.3593369396196588</v>
+      </c>
+      <c r="D84">
+        <v>1.663136939619659</v>
+      </c>
+      <c r="E84">
+        <v>1.3038</v>
+      </c>
+      <c r="F84">
+        <v>1.3038</v>
+      </c>
+      <c r="G84">
+        <v>0</v>
+      </c>
+      <c r="H84">
+        <v>1.59</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>1.67</v>
+      </c>
+      <c r="K84">
+        <v>0.741</v>
+      </c>
+      <c r="L84">
+        <v>0.9289999999999999</v>
+      </c>
+      <c r="M84">
+        <v>0.05958366000000001</v>
+      </c>
+      <c r="N84">
+        <v>0.8694163399999999</v>
+      </c>
+      <c r="O84">
+        <v>0.2173540850000001</v>
+      </c>
+      <c r="P84">
+        <v>0.6520622549999998</v>
+      </c>
+      <c r="Q84">
+        <v>1.393062255</v>
+      </c>
+      <c r="R84">
+        <v>4.555555555555557</v>
+      </c>
+      <c r="S84">
+        <v>0.3686008896591985</v>
+      </c>
+      <c r="T84">
+        <v>4.874208779376282</v>
+      </c>
+      <c r="U84">
+        <v>0.0457</v>
+      </c>
+      <c r="V84">
+        <v>0.2500000000000001</v>
+      </c>
+      <c r="W84">
+        <v>0.034275</v>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y84">
+        <v>15.59152291081145</v>
+      </c>
+      <c r="Z84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>0.8300000000000001</v>
+      </c>
+      <c r="B85">
+        <v>0.09422173038979201</v>
+      </c>
+      <c r="C85">
+        <v>0.3443704034685722</v>
+      </c>
+      <c r="D85">
+        <v>1.664070403468572</v>
+      </c>
+      <c r="E85">
+        <v>1.3197</v>
+      </c>
+      <c r="F85">
+        <v>1.3197</v>
+      </c>
+      <c r="G85">
+        <v>0</v>
+      </c>
+      <c r="H85">
+        <v>1.59</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>1.67</v>
+      </c>
+      <c r="K85">
+        <v>0.741</v>
+      </c>
+      <c r="L85">
+        <v>0.9289999999999999</v>
+      </c>
+      <c r="M85">
+        <v>0.06031029000000001</v>
+      </c>
+      <c r="N85">
+        <v>0.8686897099999999</v>
+      </c>
+      <c r="O85">
+        <v>0.2171724275000001</v>
+      </c>
+      <c r="P85">
+        <v>0.6515172824999999</v>
+      </c>
+      <c r="Q85">
+        <v>1.3925172825</v>
+      </c>
+      <c r="R85">
+        <v>4.882352941176473</v>
+      </c>
+      <c r="S85">
+        <v>0.386902825822306</v>
+      </c>
+      <c r="T85">
+        <v>5.144697612859982</v>
+      </c>
+      <c r="U85">
+        <v>0.0457</v>
+      </c>
+      <c r="V85">
+        <v>0.2500000000000001</v>
+      </c>
+      <c r="W85">
+        <v>0.034275</v>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y85">
+        <v>15.40367323718722</v>
+      </c>
+      <c r="Z85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>0.84</v>
+      </c>
+      <c r="B86">
+        <v>0.09398980064092829</v>
+      </c>
+      <c r="C86">
+        <v>0.3294049157508094</v>
+      </c>
+      <c r="D86">
+        <v>1.66500491575081</v>
+      </c>
+      <c r="E86">
+        <v>1.3356</v>
+      </c>
+      <c r="F86">
+        <v>1.3356</v>
+      </c>
+      <c r="G86">
+        <v>0</v>
+      </c>
+      <c r="H86">
+        <v>1.59</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>1.67</v>
+      </c>
+      <c r="K86">
+        <v>0.741</v>
+      </c>
+      <c r="L86">
+        <v>0.9289999999999999</v>
+      </c>
+      <c r="M86">
+        <v>0.06103692000000001</v>
+      </c>
+      <c r="N86">
+        <v>0.8679630799999999</v>
+      </c>
+      <c r="O86">
+        <v>0.2169907700000001</v>
+      </c>
+      <c r="P86">
+        <v>0.6509723099999998</v>
+      </c>
+      <c r="Q86">
+        <v>1.39197231</v>
+      </c>
+      <c r="R86">
+        <v>5.249999999999999</v>
+      </c>
+      <c r="S86">
+        <v>0.4074925040058018</v>
+      </c>
+      <c r="T86">
+        <v>5.448997550529142</v>
+      </c>
+      <c r="U86">
+        <v>0.0457</v>
+      </c>
+      <c r="V86">
+        <v>0.2500000000000001</v>
+      </c>
+      <c r="W86">
+        <v>0.034275</v>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y86">
+        <v>15.22029617483975</v>
+      </c>
+      <c r="Z86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>0.85</v>
+      </c>
+      <c r="B87">
+        <v>0.09375787089206461</v>
+      </c>
+      <c r="C87">
+        <v>0.3144404782337067</v>
+      </c>
+      <c r="D87">
+        <v>1.665940478233707</v>
+      </c>
+      <c r="E87">
+        <v>1.3515</v>
+      </c>
+      <c r="F87">
+        <v>1.3515</v>
+      </c>
+      <c r="G87">
+        <v>0</v>
+      </c>
+      <c r="H87">
+        <v>1.59</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <v>1.67</v>
+      </c>
+      <c r="K87">
+        <v>0.741</v>
+      </c>
+      <c r="L87">
+        <v>0.9289999999999999</v>
+      </c>
+      <c r="M87">
+        <v>0.06176355</v>
+      </c>
+      <c r="N87">
+        <v>0.8672364499999999</v>
+      </c>
+      <c r="O87">
+        <v>0.2168091125000001</v>
+      </c>
+      <c r="P87">
+        <v>0.6504273374999998</v>
+      </c>
+      <c r="Q87">
+        <v>1.3914273375</v>
+      </c>
+      <c r="R87">
+        <v>5.666666666666666</v>
+      </c>
+      <c r="S87">
+        <v>0.430827472613764</v>
+      </c>
+      <c r="T87">
+        <v>5.793870813220861</v>
+      </c>
+      <c r="U87">
+        <v>0.0457</v>
+      </c>
+      <c r="V87">
+        <v>0.2500000000000001</v>
+      </c>
+      <c r="W87">
+        <v>0.034275</v>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y87">
+        <v>15.04123386690046</v>
+      </c>
+      <c r="Z87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>0.86</v>
+      </c>
+      <c r="B88">
+        <v>0.0935259411432009</v>
+      </c>
+      <c r="C88">
+        <v>0.2994770926885761</v>
+      </c>
+      <c r="D88">
+        <v>1.666877092688576</v>
+      </c>
+      <c r="E88">
+        <v>1.3674</v>
+      </c>
+      <c r="F88">
+        <v>1.3674</v>
+      </c>
+      <c r="G88">
+        <v>0</v>
+      </c>
+      <c r="H88">
+        <v>1.59</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <v>1.67</v>
+      </c>
+      <c r="K88">
+        <v>0.741</v>
+      </c>
+      <c r="L88">
+        <v>0.9289999999999999</v>
+      </c>
+      <c r="M88">
+        <v>0.06249018000000001</v>
+      </c>
+      <c r="N88">
+        <v>0.8665098199999999</v>
+      </c>
+      <c r="O88">
+        <v>0.2166274550000001</v>
+      </c>
+      <c r="P88">
+        <v>0.6498823649999999</v>
+      </c>
+      <c r="Q88">
+        <v>1.390882365</v>
+      </c>
+      <c r="R88">
+        <v>6.142857142857142</v>
+      </c>
+      <c r="S88">
+        <v>0.4574960081657207</v>
+      </c>
+      <c r="T88">
+        <v>6.188011684868537</v>
+      </c>
+      <c r="U88">
+        <v>0.0457</v>
+      </c>
+      <c r="V88">
+        <v>0.2500000000000001</v>
+      </c>
+      <c r="W88">
+        <v>0.034275</v>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y88">
+        <v>14.86633579868069</v>
+      </c>
+      <c r="Z88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>0.87</v>
+      </c>
+      <c r="B89">
+        <v>0.09329401139433721</v>
+      </c>
+      <c r="C89">
+        <v>0.2845147608907141</v>
+      </c>
+      <c r="D89">
+        <v>1.667814760890714</v>
+      </c>
+      <c r="E89">
+        <v>1.3833</v>
+      </c>
+      <c r="F89">
+        <v>1.3833</v>
+      </c>
+      <c r="G89">
+        <v>0</v>
+      </c>
+      <c r="H89">
+        <v>1.59</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <v>1.67</v>
+      </c>
+      <c r="K89">
+        <v>0.741</v>
+      </c>
+      <c r="L89">
+        <v>0.9289999999999999</v>
+      </c>
+      <c r="M89">
+        <v>0.06321681</v>
+      </c>
+      <c r="N89">
+        <v>0.8657831899999999</v>
+      </c>
+      <c r="O89">
+        <v>0.2164457975000001</v>
+      </c>
+      <c r="P89">
+        <v>0.6493373924999999</v>
+      </c>
+      <c r="Q89">
+        <v>1.3903373925</v>
+      </c>
+      <c r="R89">
+        <v>6.692307692307692</v>
+      </c>
+      <c r="S89">
+        <v>0.4882673953410555</v>
+      </c>
+      <c r="T89">
+        <v>6.642789613692782</v>
+      </c>
+      <c r="U89">
+        <v>0.0457</v>
+      </c>
+      <c r="V89">
+        <v>0.2500000000000001</v>
+      </c>
+      <c r="W89">
+        <v>0.034275</v>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y89">
+        <v>14.69545837570735</v>
+      </c>
+      <c r="Z89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>0.88</v>
+      </c>
+      <c r="B90">
+        <v>0.09306208164547353</v>
+      </c>
+      <c r="C90">
+        <v>0.269553484619415</v>
+      </c>
+      <c r="D90">
+        <v>1.668753484619415</v>
+      </c>
+      <c r="E90">
+        <v>1.3992</v>
+      </c>
+      <c r="F90">
+        <v>1.3992</v>
+      </c>
+      <c r="G90">
+        <v>0</v>
+      </c>
+      <c r="H90">
+        <v>1.59</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90">
+        <v>1.67</v>
+      </c>
+      <c r="K90">
+        <v>0.741</v>
+      </c>
+      <c r="L90">
+        <v>0.9289999999999999</v>
+      </c>
+      <c r="M90">
+        <v>0.06394344</v>
+      </c>
+      <c r="N90">
+        <v>0.86505656</v>
+      </c>
+      <c r="O90">
+        <v>0.2162641400000001</v>
+      </c>
+      <c r="P90">
+        <v>0.6487924199999999</v>
+      </c>
+      <c r="Q90">
+        <v>1.38979242</v>
+      </c>
+      <c r="R90">
+        <v>7.333333333333334</v>
+      </c>
+      <c r="S90">
+        <v>0.5241673470456126</v>
+      </c>
+      <c r="T90">
+        <v>7.173363863987733</v>
+      </c>
+      <c r="U90">
+        <v>0.0457</v>
+      </c>
+      <c r="V90">
+        <v>0.2500000000000001</v>
+      </c>
+      <c r="W90">
+        <v>0.034275</v>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y90">
+        <v>14.52846453052885</v>
+      </c>
+      <c r="Z90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>0.89</v>
+      </c>
+      <c r="B91">
+        <v>0.0928301518966098</v>
+      </c>
+      <c r="C91">
+        <v>0.254593265657981</v>
+      </c>
+      <c r="D91">
+        <v>1.669693265657981</v>
+      </c>
+      <c r="E91">
+        <v>1.4151</v>
+      </c>
+      <c r="F91">
+        <v>1.4151</v>
+      </c>
+      <c r="G91">
+        <v>0</v>
+      </c>
+      <c r="H91">
+        <v>1.59</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>1.67</v>
+      </c>
+      <c r="K91">
+        <v>0.741</v>
+      </c>
+      <c r="L91">
+        <v>0.9289999999999999</v>
+      </c>
+      <c r="M91">
+        <v>0.06467007000000001</v>
+      </c>
+      <c r="N91">
+        <v>0.8643299299999999</v>
+      </c>
+      <c r="O91">
+        <v>0.2160824825000001</v>
+      </c>
+      <c r="P91">
+        <v>0.6482474474999999</v>
+      </c>
+      <c r="Q91">
+        <v>1.3892474475</v>
+      </c>
+      <c r="R91">
+        <v>8.090909090909092</v>
+      </c>
+      <c r="S91">
+        <v>0.5665945626964528</v>
+      </c>
+      <c r="T91">
+        <v>7.800406159790856</v>
+      </c>
+      <c r="U91">
+        <v>0.0457</v>
+      </c>
+      <c r="V91">
+        <v>0.2500000000000001</v>
+      </c>
+      <c r="W91">
+        <v>0.034275</v>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y91">
+        <v>14.36522335602853</v>
+      </c>
+      <c r="Z91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>0.9</v>
+      </c>
+      <c r="B92">
+        <v>0.09259822214774611</v>
+      </c>
+      <c r="C92">
+        <v>0.2396341057937332</v>
+      </c>
+      <c r="D92">
+        <v>1.670634105793733</v>
+      </c>
+      <c r="E92">
+        <v>1.431</v>
+      </c>
+      <c r="F92">
+        <v>1.431</v>
+      </c>
+      <c r="G92">
+        <v>0</v>
+      </c>
+      <c r="H92">
+        <v>1.59</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <v>1.67</v>
+      </c>
+      <c r="K92">
+        <v>0.741</v>
+      </c>
+      <c r="L92">
+        <v>0.9289999999999999</v>
+      </c>
+      <c r="M92">
+        <v>0.0653967</v>
+      </c>
+      <c r="N92">
+        <v>0.8636033</v>
+      </c>
+      <c r="O92">
+        <v>0.2159008250000001</v>
+      </c>
+      <c r="P92">
+        <v>0.6477024749999999</v>
+      </c>
+      <c r="Q92">
+        <v>1.388702475</v>
+      </c>
+      <c r="R92">
+        <v>9.000000000000002</v>
+      </c>
+      <c r="S92">
+        <v>0.6175072214774613</v>
+      </c>
+      <c r="T92">
+        <v>8.552856914754605</v>
+      </c>
+      <c r="U92">
+        <v>0.0457</v>
+      </c>
+      <c r="V92">
+        <v>0.2500000000000001</v>
+      </c>
+      <c r="W92">
+        <v>0.034275</v>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y92">
+        <v>14.20560976318377</v>
+      </c>
+      <c r="Z92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>0.91</v>
+      </c>
+      <c r="B93">
+        <v>0.09236629239888242</v>
+      </c>
+      <c r="C93">
+        <v>0.224676006818024</v>
+      </c>
+      <c r="D93">
+        <v>1.671576006818024</v>
+      </c>
+      <c r="E93">
+        <v>1.4469</v>
+      </c>
+      <c r="F93">
+        <v>1.4469</v>
+      </c>
+      <c r="G93">
+        <v>0</v>
+      </c>
+      <c r="H93">
+        <v>1.59</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="J93">
+        <v>1.67</v>
+      </c>
+      <c r="K93">
+        <v>0.741</v>
+      </c>
+      <c r="L93">
+        <v>0.9289999999999999</v>
+      </c>
+      <c r="M93">
+        <v>0.06612333000000001</v>
+      </c>
+      <c r="N93">
+        <v>0.8628766699999999</v>
+      </c>
+      <c r="O93">
+        <v>0.2157191675000001</v>
+      </c>
+      <c r="P93">
+        <v>0.6471575024999998</v>
+      </c>
+      <c r="Q93">
+        <v>1.3881575025</v>
+      </c>
+      <c r="R93">
+        <v>10.11111111111111</v>
+      </c>
+      <c r="S93">
+        <v>0.6797338044320271</v>
+      </c>
+      <c r="T93">
+        <v>9.472518948599189</v>
+      </c>
+      <c r="U93">
+        <v>0.0457</v>
+      </c>
+      <c r="V93">
+        <v>0.2500000000000001</v>
+      </c>
+      <c r="W93">
+        <v>0.034275</v>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y93">
+        <v>14.04950416139054</v>
+      </c>
+      <c r="Z93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>0.92</v>
+      </c>
+      <c r="B94">
+        <v>0.09213436265001872</v>
+      </c>
+      <c r="C94">
+        <v>0.2097189705262481</v>
+      </c>
+      <c r="D94">
+        <v>1.672518970526248</v>
+      </c>
+      <c r="E94">
+        <v>1.4628</v>
+      </c>
+      <c r="F94">
+        <v>1.4628</v>
+      </c>
+      <c r="G94">
+        <v>0</v>
+      </c>
+      <c r="H94">
+        <v>1.59</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <v>1.67</v>
+      </c>
+      <c r="K94">
+        <v>0.741</v>
+      </c>
+      <c r="L94">
+        <v>0.9289999999999999</v>
+      </c>
+      <c r="M94">
+        <v>0.06684996000000001</v>
+      </c>
+      <c r="N94">
+        <v>0.86215004</v>
+      </c>
+      <c r="O94">
+        <v>0.2155375100000001</v>
+      </c>
+      <c r="P94">
+        <v>0.6466125299999999</v>
+      </c>
+      <c r="Q94">
+        <v>1.38761253</v>
+      </c>
+      <c r="R94">
+        <v>11.50000000000001</v>
+      </c>
+      <c r="S94">
+        <v>0.7575170331252343</v>
+      </c>
+      <c r="T94">
+        <v>10.62209649090492</v>
+      </c>
+      <c r="U94">
+        <v>0.0457</v>
+      </c>
+      <c r="V94">
+        <v>0.2500000000000001</v>
+      </c>
+      <c r="W94">
+        <v>0.034275</v>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y94">
+        <v>13.89679215963629</v>
+      </c>
+      <c r="Z94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>0.93</v>
+      </c>
+      <c r="B95">
+        <v>0.09190243290115503</v>
+      </c>
+      <c r="C95">
+        <v>0.1947629987178527</v>
+      </c>
+      <c r="D95">
+        <v>1.673462998717853</v>
+      </c>
+      <c r="E95">
+        <v>1.4787</v>
+      </c>
+      <c r="F95">
+        <v>1.4787</v>
+      </c>
+      <c r="G95">
+        <v>0</v>
+      </c>
+      <c r="H95">
+        <v>1.59</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <v>1.67</v>
+      </c>
+      <c r="K95">
+        <v>0.741</v>
+      </c>
+      <c r="L95">
+        <v>0.9289999999999999</v>
+      </c>
+      <c r="M95">
+        <v>0.06757659000000001</v>
+      </c>
+      <c r="N95">
+        <v>0.8614234099999999</v>
+      </c>
+      <c r="O95">
+        <v>0.2153558525000001</v>
+      </c>
+      <c r="P95">
+        <v>0.6460675574999999</v>
+      </c>
+      <c r="Q95">
+        <v>1.3870675575</v>
+      </c>
+      <c r="R95">
+        <v>13.2857142857143</v>
+      </c>
+      <c r="S95">
+        <v>0.8575240414450724</v>
+      </c>
+      <c r="T95">
+        <v>12.10012475958371</v>
+      </c>
+      <c r="U95">
+        <v>0.0457</v>
+      </c>
+      <c r="V95">
+        <v>0.2500000000000001</v>
+      </c>
+      <c r="W95">
+        <v>0.034275</v>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y95">
+        <v>13.74736428695203</v>
+      </c>
+      <c r="Z95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="B96">
+        <v>0.09167050315229133</v>
+      </c>
+      <c r="C96">
+        <v>0.1798080931963515</v>
+      </c>
+      <c r="D96">
+        <v>1.674408093196352</v>
+      </c>
+      <c r="E96">
+        <v>1.4946</v>
+      </c>
+      <c r="F96">
+        <v>1.4946</v>
+      </c>
+      <c r="G96">
+        <v>0</v>
+      </c>
+      <c r="H96">
+        <v>1.59</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="J96">
+        <v>1.67</v>
+      </c>
+      <c r="K96">
+        <v>0.741</v>
+      </c>
+      <c r="L96">
+        <v>0.9289999999999999</v>
+      </c>
+      <c r="M96">
+        <v>0.06830322000000001</v>
+      </c>
+      <c r="N96">
+        <v>0.8606967799999999</v>
+      </c>
+      <c r="O96">
+        <v>0.2151741950000001</v>
+      </c>
+      <c r="P96">
+        <v>0.6455225849999999</v>
+      </c>
+      <c r="Q96">
+        <v>1.386522585</v>
+      </c>
+      <c r="R96">
+        <v>15.66666666666668</v>
+      </c>
+      <c r="S96">
+        <v>0.9908667192048564</v>
+      </c>
+      <c r="T96">
+        <v>14.0708291178221</v>
+      </c>
+      <c r="U96">
+        <v>0.0457</v>
+      </c>
+      <c r="V96">
+        <v>0.2500000000000001</v>
+      </c>
+      <c r="W96">
+        <v>0.034275</v>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y96">
+        <v>13.60111573070786</v>
+      </c>
+      <c r="Z96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>0.9500000000000001</v>
+      </c>
+      <c r="B97">
+        <v>0.09143857340342762</v>
+      </c>
+      <c r="C97">
+        <v>0.1648542557693338</v>
+      </c>
+      <c r="D97">
+        <v>1.675354255769334</v>
+      </c>
+      <c r="E97">
+        <v>1.5105</v>
+      </c>
+      <c r="F97">
+        <v>1.5105</v>
+      </c>
+      <c r="G97">
+        <v>0</v>
+      </c>
+      <c r="H97">
+        <v>1.59</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="J97">
+        <v>1.67</v>
+      </c>
+      <c r="K97">
+        <v>0.741</v>
+      </c>
+      <c r="L97">
+        <v>0.9289999999999999</v>
+      </c>
+      <c r="M97">
+        <v>0.06902985000000002</v>
+      </c>
+      <c r="N97">
+        <v>0.8599701499999999</v>
+      </c>
+      <c r="O97">
+        <v>0.2149925375000001</v>
+      </c>
+      <c r="P97">
+        <v>0.6449776124999999</v>
+      </c>
+      <c r="Q97">
+        <v>1.3859776125</v>
+      </c>
+      <c r="R97">
+        <v>19.00000000000003</v>
+      </c>
+      <c r="S97">
+        <v>1.177546468068554</v>
+      </c>
+      <c r="T97">
+        <v>16.82981521935586</v>
+      </c>
+      <c r="U97">
+        <v>0.0457</v>
+      </c>
+      <c r="V97">
+        <v>0.2500000000000001</v>
+      </c>
+      <c r="W97">
+        <v>0.034275</v>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y97">
+        <v>13.45794609143725</v>
+      </c>
+      <c r="Z97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>0.96</v>
+      </c>
+      <c r="B98">
+        <v>0.09120664365456393</v>
+      </c>
+      <c r="C98">
+        <v>0.1499014882484764</v>
+      </c>
+      <c r="D98">
+        <v>1.676301488248476</v>
+      </c>
+      <c r="E98">
+        <v>1.5264</v>
+      </c>
+      <c r="F98">
+        <v>1.5264</v>
+      </c>
+      <c r="G98">
+        <v>0</v>
+      </c>
+      <c r="H98">
+        <v>1.59</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>1.67</v>
+      </c>
+      <c r="K98">
+        <v>0.741</v>
+      </c>
+      <c r="L98">
+        <v>0.9289999999999999</v>
+      </c>
+      <c r="M98">
+        <v>0.06975648000000001</v>
+      </c>
+      <c r="N98">
+        <v>0.8592435199999999</v>
+      </c>
+      <c r="O98">
+        <v>0.2148108800000001</v>
+      </c>
+      <c r="P98">
+        <v>0.6444326399999999</v>
+      </c>
+      <c r="Q98">
+        <v>1.38543264</v>
+      </c>
+      <c r="R98">
+        <v>23.99999999999998</v>
+      </c>
+      <c r="S98">
+        <v>1.457566091364097</v>
+      </c>
+      <c r="T98">
+        <v>20.96829437165643</v>
+      </c>
+      <c r="U98">
+        <v>0.0457</v>
+      </c>
+      <c r="V98">
+        <v>0.2500000000000001</v>
+      </c>
+      <c r="W98">
+        <v>0.034275</v>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y98">
+        <v>13.31775915298478</v>
+      </c>
+      <c r="Z98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>0.97</v>
+      </c>
+      <c r="B99">
+        <v>0.09097471390570024</v>
+      </c>
+      <c r="C99">
+        <v>0.1349497924495564</v>
+      </c>
+      <c r="D99">
+        <v>1.677249792449556</v>
+      </c>
+      <c r="E99">
+        <v>1.5423</v>
+      </c>
+      <c r="F99">
+        <v>1.5423</v>
+      </c>
+      <c r="G99">
+        <v>0</v>
+      </c>
+      <c r="H99">
+        <v>1.59</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>1.67</v>
+      </c>
+      <c r="K99">
+        <v>0.741</v>
+      </c>
+      <c r="L99">
+        <v>0.9289999999999999</v>
+      </c>
+      <c r="M99">
+        <v>0.07048311</v>
+      </c>
+      <c r="N99">
+        <v>0.85851689</v>
+      </c>
+      <c r="O99">
+        <v>0.2146292225000001</v>
+      </c>
+      <c r="P99">
+        <v>0.6438876674999999</v>
+      </c>
+      <c r="Q99">
+        <v>1.3848876675</v>
+      </c>
+      <c r="R99">
+        <v>32.33333333333331</v>
+      </c>
+      <c r="S99">
+        <v>1.92426546352334</v>
+      </c>
+      <c r="T99">
+        <v>27.86575962549078</v>
+      </c>
+      <c r="U99">
+        <v>0.0457</v>
+      </c>
+      <c r="V99">
+        <v>0.2500000000000001</v>
+      </c>
+      <c r="W99">
+        <v>0.034275</v>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y99">
+        <v>13.18046266687154</v>
+      </c>
+      <c r="Z99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>0.98</v>
+      </c>
+      <c r="B100">
+        <v>0.09074278415683655</v>
+      </c>
+      <c r="C100">
+        <v>0.1199991701924616</v>
+      </c>
+      <c r="D100">
+        <v>1.678199170192462</v>
+      </c>
+      <c r="E100">
+        <v>1.5582</v>
+      </c>
+      <c r="F100">
+        <v>1.5582</v>
+      </c>
+      <c r="G100">
+        <v>0</v>
+      </c>
+      <c r="H100">
+        <v>1.59</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <v>1.67</v>
+      </c>
+      <c r="K100">
+        <v>0.741</v>
+      </c>
+      <c r="L100">
+        <v>0.9289999999999999</v>
+      </c>
+      <c r="M100">
+        <v>0.07120974000000001</v>
+      </c>
+      <c r="N100">
+        <v>0.8577902599999999</v>
+      </c>
+      <c r="O100">
+        <v>0.2144475650000001</v>
+      </c>
+      <c r="P100">
+        <v>0.6433426949999999</v>
+      </c>
+      <c r="Q100">
+        <v>1.384342695</v>
+      </c>
+      <c r="R100">
+        <v>48.99999999999996</v>
+      </c>
+      <c r="S100">
+        <v>2.857664207841825</v>
+      </c>
+      <c r="T100">
+        <v>41.66069013315949</v>
+      </c>
+      <c r="U100">
+        <v>0.0457</v>
+      </c>
+      <c r="V100">
+        <v>0.2500000000000001</v>
+      </c>
+      <c r="W100">
+        <v>0.034275</v>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y100">
+        <v>13.04596814986264</v>
+      </c>
+      <c r="Z100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>0.99</v>
+      </c>
+      <c r="B101">
+        <v>0.09169885440797285</v>
+      </c>
+      <c r="C101">
+        <v>0.1001925069165135</v>
+      </c>
+      <c r="D101">
+        <v>1.674292506916514</v>
+      </c>
+      <c r="E101">
+        <v>1.5741</v>
+      </c>
+      <c r="F101">
+        <v>1.5741</v>
+      </c>
+      <c r="G101">
+        <v>0</v>
+      </c>
+      <c r="H101">
+        <v>1.59</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <v>1.67</v>
+      </c>
+      <c r="K101">
+        <v>0.741</v>
+      </c>
+      <c r="L101">
+        <v>0.9289999999999999</v>
+      </c>
+      <c r="M101">
+        <v>0.07445493</v>
+      </c>
+      <c r="N101">
+        <v>0.8545450699999999</v>
+      </c>
+      <c r="O101">
+        <v>0.2136362675000001</v>
+      </c>
+      <c r="P101">
+        <v>0.6409088024999998</v>
+      </c>
+      <c r="Q101">
+        <v>1.3819088025</v>
+      </c>
+      <c r="R101">
+        <v>98.99999999999991</v>
+      </c>
+      <c r="S101">
+        <v>5.65786044079728</v>
+      </c>
+      <c r="T101">
+        <v>83.04548165616561</v>
+      </c>
+      <c r="U101">
+        <v>0.0473</v>
+      </c>
+      <c r="V101">
+        <v>0.2500000000000001</v>
+      </c>
+      <c r="W101">
+        <v>0.03547499999999999</v>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y101">
+        <v>12.47734703397075</v>
+      </c>
+      <c r="Z101">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
